--- a/Export/Coring_data_export.xlsx
+++ b/Export/Coring_data_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="13464" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="73184" uniqueCount="184">
   <si>
     <t>Event label</t>
   </si>
@@ -612,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W464"/>
+  <dimension ref="A1:W429"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="true"/>
@@ -5368,7 +5368,9 @@
       <c r="N68" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O68" s="0"/>
+      <c r="O68" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P68" s="0">
         <v>-23</v>
       </c>
@@ -5421,7 +5423,9 @@
       <c r="N69" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O69" s="0"/>
+      <c r="O69" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P69" s="0">
         <v>-23</v>
       </c>
@@ -5474,7 +5478,9 @@
       <c r="N70" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O70" s="0"/>
+      <c r="O70" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P70" s="0">
         <v>-23</v>
       </c>
@@ -5527,7 +5533,9 @@
       <c r="N71" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O71" s="0"/>
+      <c r="O71" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P71" s="0">
         <v>-23</v>
       </c>
@@ -5580,7 +5588,9 @@
       <c r="N72" s="0">
         <v>0.25</v>
       </c>
-      <c r="O72" s="0"/>
+      <c r="O72" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P72" s="0">
         <v>-23</v>
       </c>
@@ -5633,7 +5643,9 @@
       <c r="N73" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O73" s="0"/>
+      <c r="O73" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P73" s="0">
         <v>-23</v>
       </c>
@@ -5686,7 +5698,9 @@
       <c r="N74" s="0">
         <v>0.34999999999999998</v>
       </c>
-      <c r="O74" s="0"/>
+      <c r="O74" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P74" s="0">
         <v>-23</v>
       </c>
@@ -5739,7 +5753,9 @@
       <c r="N75" s="0">
         <v>0.40000000000000002</v>
       </c>
-      <c r="O75" s="0"/>
+      <c r="O75" s="0">
+        <v>0.16</v>
+      </c>
       <c r="P75" s="0">
         <v>-23</v>
       </c>
@@ -5792,7 +5808,9 @@
       <c r="N76" s="0">
         <v>0.41999999999999998</v>
       </c>
-      <c r="O76" s="0"/>
+      <c r="O76" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P76" s="0">
         <v>-23</v>
       </c>
@@ -5847,7 +5865,9 @@
       <c r="N77" s="0">
         <v>0.47999999999999998</v>
       </c>
-      <c r="O77" s="0"/>
+      <c r="O77" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P77" s="0">
         <v>-23</v>
       </c>
@@ -22559,7 +22579,9 @@
       <c r="N317" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O317" s="0"/>
+      <c r="O317" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P317" s="0">
         <v>-24</v>
       </c>
@@ -22569,13 +22591,17 @@
       <c r="R317" s="0">
         <v>885.50999999999999</v>
       </c>
-      <c r="S317" s="0"/>
-      <c r="T317" s="0"/>
+      <c r="S317" s="0">
+        <v>882.29999999999995</v>
+      </c>
+      <c r="T317" s="0">
+        <v>0.14999999999999999</v>
+      </c>
       <c r="U317" s="0">
-        <v>0</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="V317" s="0">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="W317" s="0" t="s">
         <v>132</v>
@@ -22624,7 +22650,9 @@
       <c r="N318" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O318" s="0"/>
+      <c r="O318" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P318" s="0">
         <v>-24</v>
       </c>
@@ -22634,13 +22662,17 @@
       <c r="R318" s="0">
         <v>845.02999999999997</v>
       </c>
-      <c r="S318" s="0"/>
-      <c r="T318" s="0"/>
+      <c r="S318" s="0">
+        <v>841.96000000000004</v>
+      </c>
+      <c r="T318" s="0">
+        <v>0.11</v>
+      </c>
       <c r="U318" s="0">
-        <v>0</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="V318" s="0">
-        <v>0</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="W318" s="0" t="s">
         <v>105</v>
@@ -22690,7 +22722,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O319" s="0">
-        <v>0.59999999999999998</v>
+        <v>0.17000000000000001</v>
       </c>
       <c r="P319" s="0">
         <v>-24</v>
@@ -22705,13 +22737,13 @@
         <v>869.42999999999995</v>
       </c>
       <c r="T319" s="0">
-        <v>0.28999999999999998</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="U319" s="0">
         <v>0.050000000000000003</v>
       </c>
       <c r="V319" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="W319" s="0" t="s">
         <v>105</v>
@@ -22761,7 +22793,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="O320" s="0">
-        <v>0.29999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P320" s="0">
         <v>-24</v>
@@ -22776,13 +22808,13 @@
         <v>836.09000000000003</v>
       </c>
       <c r="T320" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="U320" s="0">
         <v>0.089999999999999997</v>
       </c>
       <c r="V320" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="W320" s="0" t="s">
         <v>133</v>
@@ -22832,7 +22864,7 @@
         <v>0.25</v>
       </c>
       <c r="O321" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="P321" s="0">
         <v>-24</v>
@@ -22847,7 +22879,7 @@
         <v>845.62</v>
       </c>
       <c r="T321" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U321" s="0">
         <v>0.080000000000000002</v>
@@ -22903,7 +22935,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="O322" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="P322" s="0">
         <v>-24</v>
@@ -22918,7 +22950,7 @@
         <v>867.24000000000001</v>
       </c>
       <c r="T322" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="U322" s="0">
         <v>0.050000000000000003</v>
@@ -22974,7 +23006,7 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="O323" s="0">
-        <v>0.19</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P323" s="0">
         <v>-24</v>
@@ -22989,13 +23021,13 @@
         <v>890.75</v>
       </c>
       <c r="T323" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="U323" s="0">
         <v>0.029999999999999999</v>
       </c>
       <c r="V323" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="W323" s="0" t="s">
         <v>135</v>
@@ -23045,7 +23077,7 @@
         <v>0.40000000000000002</v>
       </c>
       <c r="O324" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="P324" s="0">
         <v>-24</v>
@@ -23060,7 +23092,7 @@
         <v>899.65999999999997</v>
       </c>
       <c r="T324" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="U324" s="0">
         <v>0.02</v>
@@ -23116,7 +23148,7 @@
         <v>0.45000000000000001</v>
       </c>
       <c r="O325" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="P325" s="0">
         <v>-24</v>
@@ -23131,7 +23163,7 @@
         <v>897.82000000000005</v>
       </c>
       <c r="T325" s="0">
-        <v>0.02</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="U325" s="0">
         <v>0.02</v>
@@ -23187,7 +23219,7 @@
         <v>0.5</v>
       </c>
       <c r="O326" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="P326" s="0">
         <v>-24</v>
@@ -23202,7 +23234,7 @@
         <v>864.26999999999998</v>
       </c>
       <c r="T326" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="U326" s="0">
         <v>0.059999999999999998</v>
@@ -23258,7 +23290,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="O327" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="P327" s="0">
         <v>-24</v>
@@ -23273,13 +23305,13 @@
         <v>900.35000000000002</v>
       </c>
       <c r="T327" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U327" s="0">
         <v>0.02</v>
       </c>
       <c r="V327" s="0">
-        <v>0.02</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="W327" s="0" t="s">
         <v>136</v>
@@ -23329,7 +23361,7 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="O328" s="0">
-        <v>0.40000000000000002</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="P328" s="0">
         <v>-24</v>
@@ -23344,13 +23376,13 @@
         <v>847.48000000000002</v>
       </c>
       <c r="T328" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U328" s="0">
         <v>0.080000000000000002</v>
       </c>
       <c r="V328" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="W328" s="0" t="s">
         <v>137</v>
@@ -23400,7 +23432,7 @@
         <v>0.65000000000000002</v>
       </c>
       <c r="O329" s="0">
-        <v>0.59999999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P329" s="0">
         <v>-24</v>
@@ -23415,7 +23447,7 @@
         <v>871.27999999999997</v>
       </c>
       <c r="T329" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.12</v>
       </c>
       <c r="U329" s="0">
         <v>0.050000000000000003</v>
@@ -23471,7 +23503,7 @@
         <v>0.69999999999999996</v>
       </c>
       <c r="O330" s="0">
-        <v>0.80000000000000004</v>
+        <v>1.3</v>
       </c>
       <c r="P330" s="0">
         <v>-24</v>
@@ -23486,13 +23518,13 @@
         <v>893.64999999999998</v>
       </c>
       <c r="T330" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.13</v>
       </c>
       <c r="U330" s="0">
         <v>0.029999999999999999</v>
       </c>
       <c r="V330" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="W330" s="0" t="s">
         <v>136</v>
@@ -23542,7 +23574,7 @@
         <v>0.75</v>
       </c>
       <c r="O331" s="0">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="P331" s="0">
         <v>-24</v>
@@ -23557,7 +23589,7 @@
         <v>896.90999999999997</v>
       </c>
       <c r="T331" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="U331" s="0">
         <v>0.02</v>
@@ -23684,7 +23716,7 @@
         <v>0.84999999999999998</v>
       </c>
       <c r="O333" s="0">
-        <v>1.3</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="P333" s="0">
         <v>-24</v>
@@ -23699,7 +23731,7 @@
         <v>891.05999999999995</v>
       </c>
       <c r="T333" s="0">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="U333" s="0">
         <v>0.029999999999999999</v>
@@ -23826,7 +23858,7 @@
         <v>0.93999999999999995</v>
       </c>
       <c r="O335" s="0">
-        <v>1.3999999999999999</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="P335" s="0">
         <v>-24</v>
@@ -23841,7 +23873,7 @@
         <v>906.13999999999999</v>
       </c>
       <c r="T335" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.17000000000000001</v>
       </c>
       <c r="U335" s="0">
         <v>0.01</v>
@@ -23897,7 +23929,7 @@
         <v>0.98999999999999999</v>
       </c>
       <c r="O336" s="0">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="P336" s="0">
         <v>-24</v>
@@ -23912,13 +23944,13 @@
         <v>898.88</v>
       </c>
       <c r="T336" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="U336" s="0">
         <v>0.02</v>
       </c>
       <c r="V336" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="W336" s="0" t="s">
         <v>139</v>
@@ -24110,7 +24142,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="O339" s="0">
-        <v>1.6000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="P339" s="0">
         <v>-24</v>
@@ -24125,7 +24157,7 @@
         <v>907.05999999999995</v>
       </c>
       <c r="T339" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="U339" s="0">
         <v>0.01</v>
@@ -24181,7 +24213,7 @@
         <v>1.1899999999999999</v>
       </c>
       <c r="O340" s="0">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P340" s="0">
         <v>-24</v>
@@ -24196,7 +24228,7 @@
         <v>910.86000000000001</v>
       </c>
       <c r="T340" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U340" s="0">
         <v>0.01</v>
@@ -24252,7 +24284,7 @@
         <v>1.24</v>
       </c>
       <c r="O341" s="0">
-        <v>1.8</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="P341" s="0">
         <v>-24</v>
@@ -24267,7 +24299,7 @@
         <v>911.91999999999996</v>
       </c>
       <c r="T341" s="0">
-        <v>0.12</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U341" s="0">
         <v>0.01</v>
@@ -24323,7 +24355,7 @@
         <v>1.29</v>
       </c>
       <c r="O342" s="0">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P342" s="0">
         <v>-24</v>
@@ -24338,7 +24370,7 @@
         <v>911.49000000000001</v>
       </c>
       <c r="T342" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.11</v>
       </c>
       <c r="U342" s="0">
         <v>0.01</v>
@@ -24394,7 +24426,7 @@
         <v>1.3400000000000001</v>
       </c>
       <c r="O343" s="0">
-        <v>1.3999999999999999</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P343" s="0">
         <v>-24</v>
@@ -24409,13 +24441,13 @@
         <v>904.61000000000001</v>
       </c>
       <c r="T343" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.13</v>
       </c>
       <c r="U343" s="0">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="V343" s="0">
-        <v>0.02</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="W343" s="0" t="s">
         <v>140</v>
@@ -24465,7 +24497,7 @@
         <v>1.3899999999999999</v>
       </c>
       <c r="O344" s="0">
-        <v>1.8</v>
+        <v>2.3999999999999999</v>
       </c>
       <c r="P344" s="0">
         <v>-24</v>
@@ -24480,7 +24512,7 @@
         <v>910.29999999999995</v>
       </c>
       <c r="T344" s="0">
-        <v>0.11</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="U344" s="0">
         <v>0.01</v>
@@ -24536,7 +24568,7 @@
         <v>1.4399999999999999</v>
       </c>
       <c r="O345" s="0">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="P345" s="0">
         <v>-24</v>
@@ -24551,7 +24583,7 @@
         <v>912.74000000000001</v>
       </c>
       <c r="T345" s="0">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="U345" s="0">
         <v>0.01</v>
@@ -24607,7 +24639,7 @@
         <v>1.49</v>
       </c>
       <c r="O346" s="0">
-        <v>2.3999999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="P346" s="0">
         <v>-24</v>
@@ -24678,7 +24710,7 @@
         <v>1.54</v>
       </c>
       <c r="O347" s="0">
-        <v>2.5</v>
+        <v>2.3999999999999999</v>
       </c>
       <c r="P347" s="0">
         <v>-24</v>
@@ -24693,7 +24725,7 @@
         <v>910.27999999999997</v>
       </c>
       <c r="T347" s="0">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="U347" s="0">
         <v>0.01</v>
@@ -24749,7 +24781,7 @@
         <v>1.5900000000000001</v>
       </c>
       <c r="O348" s="0">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P348" s="0">
         <v>-24</v>
@@ -24764,7 +24796,7 @@
         <v>911.70000000000005</v>
       </c>
       <c r="T348" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U348" s="0">
         <v>0.01</v>
@@ -24819,7 +24851,9 @@
       <c r="N349" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O349" s="0"/>
+      <c r="O349" s="0">
+        <v>0.5</v>
+      </c>
       <c r="P349" s="0">
         <v>-22</v>
       </c>
@@ -24878,7 +24912,9 @@
       <c r="N350" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O350" s="0"/>
+      <c r="O350" s="0">
+        <v>0.5</v>
+      </c>
       <c r="P350" s="0">
         <v>-22</v>
       </c>
@@ -24937,7 +24973,9 @@
       <c r="N351" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O351" s="0"/>
+      <c r="O351" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P351" s="0">
         <v>-22</v>
       </c>
@@ -24996,7 +25034,9 @@
       <c r="N352" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O352" s="0"/>
+      <c r="O352" s="0">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="P352" s="0">
         <v>-22</v>
       </c>
@@ -25055,7 +25095,9 @@
       <c r="N353" s="0">
         <v>0.25</v>
       </c>
-      <c r="O353" s="0"/>
+      <c r="O353" s="0">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="P353" s="0">
         <v>-22</v>
       </c>
@@ -25114,7 +25156,9 @@
       <c r="N354" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O354" s="0"/>
+      <c r="O354" s="0">
+        <v>1.3999999999999999</v>
+      </c>
       <c r="P354" s="0">
         <v>-22</v>
       </c>
@@ -25173,7 +25217,9 @@
       <c r="N355" s="0">
         <v>0.34999999999999998</v>
       </c>
-      <c r="O355" s="0"/>
+      <c r="O355" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P355" s="0">
         <v>-22</v>
       </c>
@@ -25232,7 +25278,9 @@
       <c r="N356" s="0">
         <v>0.40000000000000002</v>
       </c>
-      <c r="O356" s="0"/>
+      <c r="O356" s="0">
+        <v>2</v>
+      </c>
       <c r="P356" s="0">
         <v>-22</v>
       </c>
@@ -25291,7 +25339,9 @@
       <c r="N357" s="0">
         <v>0.46999999999999997</v>
       </c>
-      <c r="O357" s="0"/>
+      <c r="O357" s="0">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="P357" s="0">
         <v>-22</v>
       </c>
@@ -25350,7 +25400,9 @@
       <c r="N358" s="0">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O358" s="0"/>
+      <c r="O358" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P358" s="0">
         <v>-22</v>
       </c>
@@ -25405,7 +25457,9 @@
       <c r="N359" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O359" s="0"/>
+      <c r="O359" s="0">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="P359" s="0"/>
       <c r="Q359" s="0"/>
       <c r="R359" s="0">
@@ -25458,7 +25512,9 @@
       <c r="N360" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O360" s="0"/>
+      <c r="O360" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P360" s="0"/>
       <c r="Q360" s="0"/>
       <c r="R360" s="0">
@@ -25511,7 +25567,9 @@
       <c r="N361" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O361" s="0"/>
+      <c r="O361" s="0">
+        <v>1.8999999999999999</v>
+      </c>
       <c r="P361" s="0"/>
       <c r="Q361" s="0"/>
       <c r="R361" s="0">
@@ -25562,7 +25620,9 @@
       <c r="N362" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O362" s="0"/>
+      <c r="O362" s="0">
+        <v>1.8999999999999999</v>
+      </c>
       <c r="P362" s="0"/>
       <c r="Q362" s="0"/>
       <c r="R362" s="0">
@@ -25615,7 +25675,9 @@
       <c r="N363" s="0">
         <v>0.26000000000000001</v>
       </c>
-      <c r="O363" s="0"/>
+      <c r="O363" s="0">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="P363" s="0"/>
       <c r="Q363" s="0"/>
       <c r="R363" s="0">
@@ -25668,7 +25730,9 @@
       <c r="N364" s="0">
         <v>0.32000000000000001</v>
       </c>
-      <c r="O364" s="0"/>
+      <c r="O364" s="0">
+        <v>2.3999999999999999</v>
+      </c>
       <c r="P364" s="0"/>
       <c r="Q364" s="0"/>
       <c r="R364" s="0">
@@ -25719,7 +25783,9 @@
       <c r="N365" s="0">
         <v>0.059999999999999998</v>
       </c>
-      <c r="O365" s="0"/>
+      <c r="O365" s="0">
+        <v>1.5</v>
+      </c>
       <c r="P365" s="0">
         <v>-23</v>
       </c>
@@ -25774,7 +25840,9 @@
       <c r="N366" s="0">
         <v>0.12</v>
       </c>
-      <c r="O366" s="0"/>
+      <c r="O366" s="0">
+        <v>1.5</v>
+      </c>
       <c r="P366" s="0">
         <v>-23</v>
       </c>
@@ -25829,7 +25897,9 @@
       <c r="N367" s="0">
         <v>0.17999999999999999</v>
       </c>
-      <c r="O367" s="0"/>
+      <c r="O367" s="0">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="P367" s="0">
         <v>-23</v>
       </c>
@@ -25882,7 +25952,9 @@
       <c r="N368" s="0">
         <v>0.23999999999999999</v>
       </c>
-      <c r="O368" s="0"/>
+      <c r="O368" s="0">
+        <v>1.8999999999999999</v>
+      </c>
       <c r="P368" s="0">
         <v>-23</v>
       </c>
@@ -25937,7 +26009,9 @@
       <c r="N369" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O369" s="0"/>
+      <c r="O369" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P369" s="0">
         <v>-23</v>
       </c>
@@ -25992,7 +26066,9 @@
       <c r="N370" s="0">
         <v>0.34999999999999998</v>
       </c>
-      <c r="O370" s="0"/>
+      <c r="O370" s="0">
+        <v>1.5</v>
+      </c>
       <c r="P370" s="0">
         <v>-23</v>
       </c>
@@ -26045,7 +26121,9 @@
       <c r="N371" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O371" s="0"/>
+      <c r="O371" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P371" s="0">
         <v>-22</v>
       </c>
@@ -26100,7 +26178,9 @@
       <c r="N372" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O372" s="0"/>
+      <c r="O372" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P372" s="0">
         <v>-22</v>
       </c>
@@ -26155,7 +26235,9 @@
       <c r="N373" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O373" s="0"/>
+      <c r="O373" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P373" s="0">
         <v>-22</v>
       </c>
@@ -26210,7 +26292,9 @@
       <c r="N374" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O374" s="0"/>
+      <c r="O374" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P374" s="0">
         <v>-22</v>
       </c>
@@ -26265,7 +26349,9 @@
       <c r="N375" s="0">
         <v>0.25</v>
       </c>
-      <c r="O375" s="0"/>
+      <c r="O375" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P375" s="0">
         <v>-22</v>
       </c>
@@ -26320,7 +26406,9 @@
       <c r="N376" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O376" s="0"/>
+      <c r="O376" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P376" s="0">
         <v>-22</v>
       </c>
@@ -26375,7 +26463,9 @@
       <c r="N377" s="0">
         <v>0.34999999999999998</v>
       </c>
-      <c r="O377" s="0"/>
+      <c r="O377" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P377" s="0">
         <v>-22</v>
       </c>
@@ -26430,7 +26520,9 @@
       <c r="N378" s="0">
         <v>0.40000000000000002</v>
       </c>
-      <c r="O378" s="0"/>
+      <c r="O378" s="0">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="P378" s="0">
         <v>-22</v>
       </c>
@@ -26485,7 +26577,9 @@
       <c r="N379" s="0">
         <v>0.45000000000000001</v>
       </c>
-      <c r="O379" s="0"/>
+      <c r="O379" s="0">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="P379" s="0">
         <v>-22</v>
       </c>
@@ -26540,7 +26634,9 @@
       <c r="N380" s="0">
         <v>0.5</v>
       </c>
-      <c r="O380" s="0"/>
+      <c r="O380" s="0">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="P380" s="0">
         <v>-22</v>
       </c>
@@ -26595,7 +26691,9 @@
       <c r="N381" s="0">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O381" s="0"/>
+      <c r="O381" s="0">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="P381" s="0">
         <v>-22</v>
       </c>
@@ -26650,7 +26748,9 @@
       <c r="N382" s="0">
         <v>0.59999999999999998</v>
       </c>
-      <c r="O382" s="0"/>
+      <c r="O382" s="0">
+        <v>1.2</v>
+      </c>
       <c r="P382" s="0">
         <v>-22</v>
       </c>
@@ -26705,7 +26805,9 @@
       <c r="N383" s="0">
         <v>0.66000000000000003</v>
       </c>
-      <c r="O383" s="0"/>
+      <c r="O383" s="0">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="P383" s="0">
         <v>-22</v>
       </c>
@@ -26760,7 +26862,9 @@
       <c r="N384" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O384" s="0"/>
+      <c r="O384" s="0">
+        <v>0.5</v>
+      </c>
       <c r="P384" s="0">
         <v>-22</v>
       </c>
@@ -26815,7 +26919,9 @@
       <c r="N385" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O385" s="0"/>
+      <c r="O385" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P385" s="0">
         <v>-22</v>
       </c>
@@ -26870,7 +26976,9 @@
       <c r="N386" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O386" s="0"/>
+      <c r="O386" s="0">
+        <v>1.2</v>
+      </c>
       <c r="P386" s="0">
         <v>-22</v>
       </c>
@@ -26925,7 +27033,9 @@
       <c r="N387" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O387" s="0"/>
+      <c r="O387" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P387" s="0">
         <v>-22</v>
       </c>
@@ -26980,7 +27090,9 @@
       <c r="N388" s="0">
         <v>0.27000000000000002</v>
       </c>
-      <c r="O388" s="0"/>
+      <c r="O388" s="0">
+        <v>1.8</v>
+      </c>
       <c r="P388" s="0">
         <v>-22</v>
       </c>
@@ -27001,22 +27113,18 @@
         <v>181</v>
       </c>
       <c r="B389" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C389" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D389" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C389" s="0"/>
+      <c r="D389" s="0"/>
       <c r="E389" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F389" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G389" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H389" s="0">
         <v>21</v>
@@ -27039,20 +27147,22 @@
       <c r="N389" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O389" s="0"/>
+      <c r="O389" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P389" s="0">
         <v>-22</v>
       </c>
       <c r="Q389" s="0"/>
       <c r="R389" s="0">
-        <v>867.25999999999999</v>
+        <v>835</v>
       </c>
       <c r="S389" s="0"/>
       <c r="T389" s="0"/>
       <c r="U389" s="0"/>
       <c r="V389" s="0"/>
       <c r="W389" s="0" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
     </row>
     <row r="390">
@@ -27060,22 +27170,18 @@
         <v>181</v>
       </c>
       <c r="B390" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C390" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D390" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C390" s="0"/>
+      <c r="D390" s="0"/>
       <c r="E390" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F390" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G390" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H390" s="0">
         <v>21</v>
@@ -27098,20 +27204,22 @@
       <c r="N390" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O390" s="0"/>
+      <c r="O390" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P390" s="0">
         <v>-22</v>
       </c>
       <c r="Q390" s="0"/>
       <c r="R390" s="0">
-        <v>883.63999999999999</v>
+        <v>840.02999999999997</v>
       </c>
       <c r="S390" s="0"/>
       <c r="T390" s="0"/>
       <c r="U390" s="0"/>
       <c r="V390" s="0"/>
       <c r="W390" s="0" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
     </row>
     <row r="391">
@@ -27119,22 +27227,18 @@
         <v>181</v>
       </c>
       <c r="B391" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C391" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D391" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C391" s="0"/>
+      <c r="D391" s="0"/>
       <c r="E391" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F391" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G391" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H391" s="0">
         <v>21</v>
@@ -27157,20 +27261,22 @@
       <c r="N391" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O391" s="0"/>
+      <c r="O391" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P391" s="0">
         <v>-22</v>
       </c>
       <c r="Q391" s="0"/>
       <c r="R391" s="0">
-        <v>898.64999999999998</v>
+        <v>836.58000000000004</v>
       </c>
       <c r="S391" s="0"/>
       <c r="T391" s="0"/>
       <c r="U391" s="0"/>
       <c r="V391" s="0"/>
       <c r="W391" s="0" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
     </row>
     <row r="392">
@@ -27178,22 +27284,18 @@
         <v>181</v>
       </c>
       <c r="B392" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C392" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D392" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C392" s="0"/>
+      <c r="D392" s="0"/>
       <c r="E392" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F392" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G392" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H392" s="0">
         <v>21</v>
@@ -27214,22 +27316,24 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="N392" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="O392" s="0"/>
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="O392" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P392" s="0">
         <v>-22</v>
       </c>
       <c r="Q392" s="0"/>
       <c r="R392" s="0">
-        <v>876.25999999999999</v>
+        <v>835</v>
       </c>
       <c r="S392" s="0"/>
       <c r="T392" s="0"/>
       <c r="U392" s="0"/>
       <c r="V392" s="0"/>
       <c r="W392" s="0" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
     </row>
     <row r="393">
@@ -27237,22 +27341,18 @@
         <v>181</v>
       </c>
       <c r="B393" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C393" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D393" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C393" s="0"/>
+      <c r="D393" s="0"/>
       <c r="E393" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F393" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G393" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H393" s="0">
         <v>21</v>
@@ -27270,25 +27370,27 @@
         <v>1</v>
       </c>
       <c r="M393" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.20999999999999999</v>
       </c>
       <c r="N393" s="0">
         <v>0.25</v>
       </c>
-      <c r="O393" s="0"/>
+      <c r="O393" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P393" s="0">
         <v>-22</v>
       </c>
       <c r="Q393" s="0"/>
       <c r="R393" s="0">
-        <v>872.80999999999995</v>
+        <v>835</v>
       </c>
       <c r="S393" s="0"/>
       <c r="T393" s="0"/>
       <c r="U393" s="0"/>
       <c r="V393" s="0"/>
       <c r="W393" s="0" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
     </row>
     <row r="394">
@@ -27296,22 +27398,18 @@
         <v>181</v>
       </c>
       <c r="B394" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C394" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D394" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C394" s="0"/>
+      <c r="D394" s="0"/>
       <c r="E394" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F394" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G394" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H394" s="0">
         <v>21</v>
@@ -27334,20 +27432,22 @@
       <c r="N394" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O394" s="0"/>
+      <c r="O394" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P394" s="0">
         <v>-22</v>
       </c>
       <c r="Q394" s="0"/>
       <c r="R394" s="0">
-        <v>852.58000000000004</v>
+        <v>848.88999999999999</v>
       </c>
       <c r="S394" s="0"/>
       <c r="T394" s="0"/>
       <c r="U394" s="0"/>
       <c r="V394" s="0"/>
       <c r="W394" s="0" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
     </row>
     <row r="395">
@@ -27355,22 +27455,18 @@
         <v>181</v>
       </c>
       <c r="B395" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C395" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D395" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C395" s="0"/>
+      <c r="D395" s="0"/>
       <c r="E395" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F395" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G395" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H395" s="0">
         <v>21</v>
@@ -27391,22 +27487,24 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="N395" s="0">
-        <v>0.34999999999999998</v>
-      </c>
-      <c r="O395" s="0"/>
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="O395" s="0">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="P395" s="0">
         <v>-22</v>
       </c>
       <c r="Q395" s="0"/>
       <c r="R395" s="0">
-        <v>877.88999999999999</v>
+        <v>883.69000000000005</v>
       </c>
       <c r="S395" s="0"/>
       <c r="T395" s="0"/>
       <c r="U395" s="0"/>
       <c r="V395" s="0"/>
       <c r="W395" s="0" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="396">
@@ -27414,22 +27512,18 @@
         <v>181</v>
       </c>
       <c r="B396" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C396" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D396" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C396" s="0"/>
+      <c r="D396" s="0"/>
       <c r="E396" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F396" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G396" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H396" s="0">
         <v>21</v>
@@ -27447,25 +27541,27 @@
         <v>1</v>
       </c>
       <c r="M396" s="0">
-        <v>0.34999999999999998</v>
+        <v>0.35999999999999999</v>
       </c>
       <c r="N396" s="0">
         <v>0.40000000000000002</v>
       </c>
-      <c r="O396" s="0"/>
+      <c r="O396" s="0">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="P396" s="0">
         <v>-22</v>
       </c>
       <c r="Q396" s="0"/>
       <c r="R396" s="0">
-        <v>882.07000000000005</v>
+        <v>868.80999999999995</v>
       </c>
       <c r="S396" s="0"/>
       <c r="T396" s="0"/>
       <c r="U396" s="0"/>
       <c r="V396" s="0"/>
       <c r="W396" s="0" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="397">
@@ -27473,22 +27569,18 @@
         <v>181</v>
       </c>
       <c r="B397" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C397" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D397" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C397" s="0"/>
+      <c r="D397" s="0"/>
       <c r="E397" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F397" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G397" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H397" s="0">
         <v>21</v>
@@ -27511,20 +27603,22 @@
       <c r="N397" s="0">
         <v>0.45000000000000001</v>
       </c>
-      <c r="O397" s="0"/>
+      <c r="O397" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P397" s="0">
         <v>-22</v>
       </c>
       <c r="Q397" s="0"/>
       <c r="R397" s="0">
-        <v>911.26999999999998</v>
+        <v>888.38999999999999</v>
       </c>
       <c r="S397" s="0"/>
       <c r="T397" s="0"/>
       <c r="U397" s="0"/>
       <c r="V397" s="0"/>
       <c r="W397" s="0" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
     </row>
     <row r="398">
@@ -27532,22 +27626,18 @@
         <v>181</v>
       </c>
       <c r="B398" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C398" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D398" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C398" s="0"/>
+      <c r="D398" s="0"/>
       <c r="E398" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F398" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G398" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H398" s="0">
         <v>21</v>
@@ -27570,20 +27660,22 @@
       <c r="N398" s="0">
         <v>0.5</v>
       </c>
-      <c r="O398" s="0"/>
+      <c r="O398" s="0">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="P398" s="0">
         <v>-22</v>
       </c>
       <c r="Q398" s="0"/>
       <c r="R398" s="0">
-        <v>888.75999999999999</v>
+        <v>907.75999999999999</v>
       </c>
       <c r="S398" s="0"/>
       <c r="T398" s="0"/>
       <c r="U398" s="0"/>
       <c r="V398" s="0"/>
       <c r="W398" s="0" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
     </row>
     <row r="399">
@@ -27591,22 +27683,18 @@
         <v>181</v>
       </c>
       <c r="B399" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C399" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D399" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C399" s="0"/>
+      <c r="D399" s="0"/>
       <c r="E399" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F399" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G399" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H399" s="0">
         <v>21</v>
@@ -27629,20 +27717,22 @@
       <c r="N399" s="0">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O399" s="0"/>
+      <c r="O399" s="0">
+        <v>0.5</v>
+      </c>
       <c r="P399" s="0">
         <v>-22</v>
       </c>
       <c r="Q399" s="0"/>
       <c r="R399" s="0">
-        <v>905.01999999999998</v>
+        <v>879.98000000000002</v>
       </c>
       <c r="S399" s="0"/>
       <c r="T399" s="0"/>
       <c r="U399" s="0"/>
       <c r="V399" s="0"/>
       <c r="W399" s="0" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="400">
@@ -27650,22 +27740,18 @@
         <v>181</v>
       </c>
       <c r="B400" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C400" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D400" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C400" s="0"/>
+      <c r="D400" s="0"/>
       <c r="E400" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F400" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G400" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H400" s="0">
         <v>21</v>
@@ -27688,20 +27774,22 @@
       <c r="N400" s="0">
         <v>0.59999999999999998</v>
       </c>
-      <c r="O400" s="0"/>
+      <c r="O400" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P400" s="0">
         <v>-22</v>
       </c>
       <c r="Q400" s="0"/>
       <c r="R400" s="0">
-        <v>907.10000000000002</v>
+        <v>877.13</v>
       </c>
       <c r="S400" s="0"/>
       <c r="T400" s="0"/>
       <c r="U400" s="0"/>
       <c r="V400" s="0"/>
       <c r="W400" s="0" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
     </row>
     <row r="401">
@@ -27709,22 +27797,18 @@
         <v>181</v>
       </c>
       <c r="B401" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C401" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D401" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C401" s="0"/>
+      <c r="D401" s="0"/>
       <c r="E401" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F401" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G401" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H401" s="0">
         <v>21</v>
@@ -27745,22 +27829,24 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="N401" s="0">
-        <v>0.65000000000000002</v>
-      </c>
-      <c r="O401" s="0"/>
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="O401" s="0">
+        <v>1</v>
+      </c>
       <c r="P401" s="0">
         <v>-22</v>
       </c>
       <c r="Q401" s="0"/>
       <c r="R401" s="0">
-        <v>904.03999999999996</v>
+        <v>909.88999999999999</v>
       </c>
       <c r="S401" s="0"/>
       <c r="T401" s="0"/>
       <c r="U401" s="0"/>
       <c r="V401" s="0"/>
       <c r="W401" s="0" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
     </row>
     <row r="402">
@@ -27768,22 +27854,18 @@
         <v>181</v>
       </c>
       <c r="B402" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C402" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D402" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C402" s="0"/>
+      <c r="D402" s="0"/>
       <c r="E402" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F402" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G402" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H402" s="0">
         <v>21</v>
@@ -27801,25 +27883,27 @@
         <v>1</v>
       </c>
       <c r="M402" s="0">
-        <v>0.65000000000000002</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="N402" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="O402" s="0"/>
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="O402" s="0">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="P402" s="0">
         <v>-22</v>
       </c>
       <c r="Q402" s="0"/>
       <c r="R402" s="0">
-        <v>906.36000000000001</v>
+        <v>919.49000000000001</v>
       </c>
       <c r="S402" s="0"/>
       <c r="T402" s="0"/>
       <c r="U402" s="0"/>
       <c r="V402" s="0"/>
       <c r="W402" s="0" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="403">
@@ -27827,22 +27911,18 @@
         <v>181</v>
       </c>
       <c r="B403" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C403" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D403" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C403" s="0"/>
+      <c r="D403" s="0"/>
       <c r="E403" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F403" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G403" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H403" s="0">
         <v>21</v>
@@ -27860,46 +27940,46 @@
         <v>1</v>
       </c>
       <c r="M403" s="0">
-        <v>0.69999999999999996</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="N403" s="0">
-        <v>0.75</v>
-      </c>
-      <c r="O403" s="0"/>
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="O403" s="0">
+        <v>1.2</v>
+      </c>
       <c r="P403" s="0">
         <v>-22</v>
       </c>
       <c r="Q403" s="0"/>
       <c r="R403" s="0">
-        <v>901.03999999999996</v>
+        <v>883.77999999999997</v>
       </c>
       <c r="S403" s="0"/>
       <c r="T403" s="0"/>
       <c r="U403" s="0"/>
       <c r="V403" s="0"/>
-      <c r="W403" s="0"/>
+      <c r="W403" s="0" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
         <v>181</v>
       </c>
       <c r="B404" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C404" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D404" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C404" s="0"/>
+      <c r="D404" s="0"/>
       <c r="E404" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F404" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G404" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H404" s="0">
         <v>21</v>
@@ -27917,25 +27997,27 @@
         <v>1</v>
       </c>
       <c r="M404" s="0">
-        <v>0.75</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="N404" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="O404" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="O404" s="0">
+        <v>1.2</v>
+      </c>
       <c r="P404" s="0">
         <v>-22</v>
       </c>
       <c r="Q404" s="0"/>
       <c r="R404" s="0">
-        <v>907.64999999999998</v>
+        <v>893.38999999999999</v>
       </c>
       <c r="S404" s="0"/>
       <c r="T404" s="0"/>
       <c r="U404" s="0"/>
       <c r="V404" s="0"/>
       <c r="W404" s="0" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
     </row>
     <row r="405">
@@ -27943,22 +28025,18 @@
         <v>181</v>
       </c>
       <c r="B405" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C405" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D405" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C405" s="0"/>
+      <c r="D405" s="0"/>
       <c r="E405" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F405" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G405" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H405" s="0">
         <v>21</v>
@@ -27976,18 +28054,20 @@
         <v>1</v>
       </c>
       <c r="M405" s="0">
-        <v>0.80000000000000004</v>
+        <v>1</v>
       </c>
       <c r="N405" s="0">
-        <v>0.84999999999999998</v>
-      </c>
-      <c r="O405" s="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O405" s="0">
+        <v>1.7</v>
+      </c>
       <c r="P405" s="0">
         <v>-22</v>
       </c>
       <c r="Q405" s="0"/>
       <c r="R405" s="0">
-        <v>899.17999999999995</v>
+        <v>900.75999999999999</v>
       </c>
       <c r="S405" s="0"/>
       <c r="T405" s="0"/>
@@ -28000,22 +28080,18 @@
         <v>181</v>
       </c>
       <c r="B406" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C406" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D406" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C406" s="0"/>
+      <c r="D406" s="0"/>
       <c r="E406" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F406" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G406" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H406" s="0">
         <v>21</v>
@@ -28033,48 +28109,44 @@
         <v>1</v>
       </c>
       <c r="M406" s="0">
-        <v>0.84999999999999998</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N406" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="O406" s="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="O406" s="0">
+        <v>1.8999999999999999</v>
+      </c>
       <c r="P406" s="0">
         <v>-22</v>
       </c>
       <c r="Q406" s="0"/>
       <c r="R406" s="0">
-        <v>895.40999999999997</v>
+        <v>919.61000000000001</v>
       </c>
       <c r="S406" s="0"/>
       <c r="T406" s="0"/>
       <c r="U406" s="0"/>
       <c r="V406" s="0"/>
-      <c r="W406" s="0" t="s">
-        <v>39</v>
-      </c>
+      <c r="W406" s="0"/>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
         <v>181</v>
       </c>
       <c r="B407" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C407" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D407" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C407" s="0"/>
+      <c r="D407" s="0"/>
       <c r="E407" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F407" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G407" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H407" s="0">
         <v>21</v>
@@ -28092,48 +28164,44 @@
         <v>1</v>
       </c>
       <c r="M407" s="0">
-        <v>0.90000000000000002</v>
+        <v>1.2</v>
       </c>
       <c r="N407" s="0">
-        <v>0.94999999999999996</v>
-      </c>
-      <c r="O407" s="0"/>
+        <v>1.26</v>
+      </c>
+      <c r="O407" s="0">
+        <v>1.6000000000000001</v>
+      </c>
       <c r="P407" s="0">
         <v>-22</v>
       </c>
       <c r="Q407" s="0"/>
       <c r="R407" s="0">
-        <v>885.00999999999999</v>
+        <v>921.37</v>
       </c>
       <c r="S407" s="0"/>
       <c r="T407" s="0"/>
       <c r="U407" s="0"/>
       <c r="V407" s="0"/>
-      <c r="W407" s="0" t="s">
-        <v>39</v>
-      </c>
+      <c r="W407" s="0"/>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
         <v>181</v>
       </c>
       <c r="B408" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C408" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D408" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45874</v>
+      </c>
+      <c r="C408" s="0"/>
+      <c r="D408" s="0"/>
       <c r="E408" s="0">
-        <v>1.72</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="F408" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="G408" s="0">
-        <v>1.76</v>
+        <v>1.325</v>
       </c>
       <c r="H408" s="0">
         <v>21</v>
@@ -28151,18 +28219,20 @@
         <v>1</v>
       </c>
       <c r="M408" s="0">
-        <v>0.94999999999999996</v>
+        <v>1.26</v>
       </c>
       <c r="N408" s="0">
-        <v>1</v>
-      </c>
-      <c r="O408" s="0"/>
+        <v>1.3200000000000001</v>
+      </c>
+      <c r="O408" s="0">
+        <v>1.5</v>
+      </c>
       <c r="P408" s="0">
         <v>-22</v>
       </c>
       <c r="Q408" s="0"/>
       <c r="R408" s="0">
-        <v>907.97000000000003</v>
+        <v>918</v>
       </c>
       <c r="S408" s="0"/>
       <c r="T408" s="0"/>
@@ -28172,34 +28242,30 @@
     </row>
     <row r="409">
       <c r="A409" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B409" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C409" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D409" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C409" s="0"/>
+      <c r="D409" s="0"/>
       <c r="E409" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F409" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G409" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H409" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I409" s="0">
         <v>3</v>
       </c>
       <c r="J409" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K409" s="0" t="s">
         <v>18</v>
@@ -28208,57 +28274,55 @@
         <v>1</v>
       </c>
       <c r="M409" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N409" s="0">
-        <v>1.05</v>
-      </c>
-      <c r="O409" s="0"/>
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="O409" s="0">
+        <v>0.12</v>
+      </c>
       <c r="P409" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q409" s="0"/>
       <c r="R409" s="0">
-        <v>914.88</v>
+        <v>879.48000000000002</v>
       </c>
       <c r="S409" s="0"/>
       <c r="T409" s="0"/>
       <c r="U409" s="0"/>
       <c r="V409" s="0"/>
       <c r="W409" s="0" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B410" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C410" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D410" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C410" s="0"/>
+      <c r="D410" s="0"/>
       <c r="E410" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F410" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G410" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H410" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I410" s="0">
         <v>3</v>
       </c>
       <c r="J410" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K410" s="0" t="s">
         <v>18</v>
@@ -28267,57 +28331,55 @@
         <v>1</v>
       </c>
       <c r="M410" s="0">
-        <v>1.05</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="N410" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="O410" s="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="O410" s="0">
+        <v>0.12</v>
+      </c>
       <c r="P410" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q410" s="0"/>
       <c r="R410" s="0">
-        <v>911.47000000000003</v>
+        <v>869.49000000000001</v>
       </c>
       <c r="S410" s="0"/>
       <c r="T410" s="0"/>
       <c r="U410" s="0"/>
       <c r="V410" s="0"/>
       <c r="W410" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B411" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C411" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D411" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C411" s="0"/>
+      <c r="D411" s="0"/>
       <c r="E411" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F411" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G411" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H411" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I411" s="0">
         <v>3</v>
       </c>
       <c r="J411" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K411" s="0" t="s">
         <v>18</v>
@@ -28326,55 +28388,55 @@
         <v>1</v>
       </c>
       <c r="M411" s="0">
-        <v>1.1000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N411" s="0">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="O411" s="0"/>
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="O411" s="0">
+        <v>0.11</v>
+      </c>
       <c r="P411" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q411" s="0"/>
       <c r="R411" s="0">
-        <v>911.95000000000005</v>
+        <v>841.63999999999999</v>
       </c>
       <c r="S411" s="0"/>
       <c r="T411" s="0"/>
       <c r="U411" s="0"/>
       <c r="V411" s="0"/>
-      <c r="W411" s="0"/>
+      <c r="W411" s="0" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B412" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C412" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D412" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C412" s="0"/>
+      <c r="D412" s="0"/>
       <c r="E412" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F412" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G412" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H412" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I412" s="0">
         <v>3</v>
       </c>
       <c r="J412" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K412" s="0" t="s">
         <v>18</v>
@@ -28383,55 +28445,55 @@
         <v>1</v>
       </c>
       <c r="M412" s="0">
-        <v>1.1499999999999999</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="N412" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="O412" s="0"/>
+        <v>0.22</v>
+      </c>
+      <c r="O412" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P412" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q412" s="0"/>
       <c r="R412" s="0">
-        <v>914.74000000000001</v>
+        <v>839.62</v>
       </c>
       <c r="S412" s="0"/>
       <c r="T412" s="0"/>
       <c r="U412" s="0"/>
       <c r="V412" s="0"/>
-      <c r="W412" s="0"/>
+      <c r="W412" s="0" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B413" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C413" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D413" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C413" s="0"/>
+      <c r="D413" s="0"/>
       <c r="E413" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F413" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G413" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H413" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I413" s="0">
         <v>3</v>
       </c>
       <c r="J413" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K413" s="0" t="s">
         <v>18</v>
@@ -28440,55 +28502,55 @@
         <v>1</v>
       </c>
       <c r="M413" s="0">
-        <v>1.2</v>
+        <v>0.22</v>
       </c>
       <c r="N413" s="0">
-        <v>1.25</v>
-      </c>
-      <c r="O413" s="0"/>
+        <v>0.27000000000000002</v>
+      </c>
+      <c r="O413" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P413" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q413" s="0"/>
       <c r="R413" s="0">
-        <v>916.5</v>
+        <v>835.5</v>
       </c>
       <c r="S413" s="0"/>
       <c r="T413" s="0"/>
       <c r="U413" s="0"/>
       <c r="V413" s="0"/>
-      <c r="W413" s="0"/>
+      <c r="W413" s="0" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B414" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C414" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D414" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C414" s="0"/>
+      <c r="D414" s="0"/>
       <c r="E414" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F414" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G414" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H414" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I414" s="0">
         <v>3</v>
       </c>
       <c r="J414" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K414" s="0" t="s">
         <v>18</v>
@@ -28497,55 +28559,55 @@
         <v>1</v>
       </c>
       <c r="M414" s="0">
-        <v>1.25</v>
+        <v>0.27000000000000002</v>
       </c>
       <c r="N414" s="0">
-        <v>1.3</v>
-      </c>
-      <c r="O414" s="0"/>
+        <v>0.33000000000000002</v>
+      </c>
+      <c r="O414" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P414" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q414" s="0"/>
       <c r="R414" s="0">
-        <v>916.01999999999998</v>
+        <v>835.5</v>
       </c>
       <c r="S414" s="0"/>
       <c r="T414" s="0"/>
       <c r="U414" s="0"/>
       <c r="V414" s="0"/>
-      <c r="W414" s="0"/>
+      <c r="W414" s="0" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B415" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C415" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D415" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C415" s="0"/>
+      <c r="D415" s="0"/>
       <c r="E415" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F415" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G415" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H415" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I415" s="0">
         <v>3</v>
       </c>
       <c r="J415" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K415" s="0" t="s">
         <v>18</v>
@@ -28554,55 +28616,55 @@
         <v>1</v>
       </c>
       <c r="M415" s="0">
-        <v>1.3</v>
+        <v>0.33000000000000002</v>
       </c>
       <c r="N415" s="0">
-        <v>1.3500000000000001</v>
-      </c>
-      <c r="O415" s="0"/>
+        <v>0.39000000000000001</v>
+      </c>
+      <c r="O415" s="0">
+        <v>0.12</v>
+      </c>
       <c r="P415" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q415" s="0"/>
       <c r="R415" s="0">
-        <v>916.98000000000002</v>
+        <v>835.5</v>
       </c>
       <c r="S415" s="0"/>
       <c r="T415" s="0"/>
       <c r="U415" s="0"/>
       <c r="V415" s="0"/>
-      <c r="W415" s="0"/>
+      <c r="W415" s="0" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B416" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C416" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D416" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C416" s="0"/>
+      <c r="D416" s="0"/>
       <c r="E416" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F416" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G416" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H416" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I416" s="0">
         <v>3</v>
       </c>
       <c r="J416" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K416" s="0" t="s">
         <v>18</v>
@@ -28611,55 +28673,55 @@
         <v>1</v>
       </c>
       <c r="M416" s="0">
-        <v>1.3500000000000001</v>
+        <v>0.39000000000000001</v>
       </c>
       <c r="N416" s="0">
-        <v>1.3999999999999999</v>
-      </c>
-      <c r="O416" s="0"/>
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="O416" s="0">
+        <v>0.12</v>
+      </c>
       <c r="P416" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q416" s="0"/>
       <c r="R416" s="0">
-        <v>917.38</v>
+        <v>841.88</v>
       </c>
       <c r="S416" s="0"/>
       <c r="T416" s="0"/>
       <c r="U416" s="0"/>
       <c r="V416" s="0"/>
-      <c r="W416" s="0"/>
+      <c r="W416" s="0" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B417" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C417" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D417" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C417" s="0"/>
+      <c r="D417" s="0"/>
       <c r="E417" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F417" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G417" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H417" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I417" s="0">
         <v>3</v>
       </c>
       <c r="J417" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K417" s="0" t="s">
         <v>18</v>
@@ -28668,55 +28730,55 @@
         <v>1</v>
       </c>
       <c r="M417" s="0">
-        <v>1.3999999999999999</v>
+        <v>0.45000000000000001</v>
       </c>
       <c r="N417" s="0">
-        <v>1.45</v>
-      </c>
-      <c r="O417" s="0"/>
+        <v>0.51000000000000001</v>
+      </c>
+      <c r="O417" s="0">
+        <v>0.12</v>
+      </c>
       <c r="P417" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q417" s="0"/>
       <c r="R417" s="0">
-        <v>914.89999999999998</v>
+        <v>835.5</v>
       </c>
       <c r="S417" s="0"/>
       <c r="T417" s="0"/>
       <c r="U417" s="0"/>
       <c r="V417" s="0"/>
-      <c r="W417" s="0"/>
+      <c r="W417" s="0" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B418" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C418" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D418" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C418" s="0"/>
+      <c r="D418" s="0"/>
       <c r="E418" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F418" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G418" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H418" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I418" s="0">
         <v>3</v>
       </c>
       <c r="J418" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K418" s="0" t="s">
         <v>18</v>
@@ -28725,55 +28787,55 @@
         <v>1</v>
       </c>
       <c r="M418" s="0">
-        <v>1.45</v>
+        <v>0.51000000000000001</v>
       </c>
       <c r="N418" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="O418" s="0"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O418" s="0">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="P418" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q418" s="0"/>
       <c r="R418" s="0">
-        <v>915.38999999999999</v>
+        <v>840.57000000000005</v>
       </c>
       <c r="S418" s="0"/>
       <c r="T418" s="0"/>
       <c r="U418" s="0"/>
       <c r="V418" s="0"/>
-      <c r="W418" s="0"/>
+      <c r="W418" s="0" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B419" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C419" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D419" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C419" s="0"/>
+      <c r="D419" s="0"/>
       <c r="E419" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F419" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G419" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H419" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I419" s="0">
         <v>3</v>
       </c>
       <c r="J419" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K419" s="0" t="s">
         <v>18</v>
@@ -28782,55 +28844,55 @@
         <v>1</v>
       </c>
       <c r="M419" s="0">
-        <v>1.5</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N419" s="0">
-        <v>1.55</v>
-      </c>
-      <c r="O419" s="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O419" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P419" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q419" s="0"/>
       <c r="R419" s="0">
-        <v>915.27999999999997</v>
+        <v>847.29999999999995</v>
       </c>
       <c r="S419" s="0"/>
       <c r="T419" s="0"/>
       <c r="U419" s="0"/>
       <c r="V419" s="0"/>
-      <c r="W419" s="0"/>
+      <c r="W419" s="0" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B420" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C420" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D420" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C420" s="0"/>
+      <c r="D420" s="0"/>
       <c r="E420" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F420" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G420" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H420" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I420" s="0">
         <v>3</v>
       </c>
       <c r="J420" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K420" s="0" t="s">
         <v>18</v>
@@ -28839,55 +28901,55 @@
         <v>1</v>
       </c>
       <c r="M420" s="0">
-        <v>1.55</v>
+        <v>0.63</v>
       </c>
       <c r="N420" s="0">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="O420" s="0"/>
+        <v>0.68999999999999995</v>
+      </c>
+      <c r="O420" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P420" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q420" s="0"/>
       <c r="R420" s="0">
-        <v>916.40999999999997</v>
+        <v>849.52999999999997</v>
       </c>
       <c r="S420" s="0"/>
       <c r="T420" s="0"/>
       <c r="U420" s="0"/>
       <c r="V420" s="0"/>
-      <c r="W420" s="0"/>
+      <c r="W420" s="0" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B421" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C421" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D421" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C421" s="0"/>
+      <c r="D421" s="0"/>
       <c r="E421" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F421" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G421" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H421" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I421" s="0">
         <v>3</v>
       </c>
       <c r="J421" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K421" s="0" t="s">
         <v>18</v>
@@ -28896,55 +28958,55 @@
         <v>1</v>
       </c>
       <c r="M421" s="0">
-        <v>1.6000000000000001</v>
+        <v>0.68999999999999995</v>
       </c>
       <c r="N421" s="0">
-        <v>1.6499999999999999</v>
-      </c>
-      <c r="O421" s="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="O421" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P421" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q421" s="0"/>
       <c r="R421" s="0">
-        <v>915.61000000000001</v>
+        <v>841.91999999999996</v>
       </c>
       <c r="S421" s="0"/>
       <c r="T421" s="0"/>
       <c r="U421" s="0"/>
       <c r="V421" s="0"/>
-      <c r="W421" s="0"/>
+      <c r="W421" s="0" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B422" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C422" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D422" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C422" s="0"/>
+      <c r="D422" s="0"/>
       <c r="E422" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F422" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G422" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H422" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I422" s="0">
         <v>3</v>
       </c>
       <c r="J422" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K422" s="0" t="s">
         <v>18</v>
@@ -28953,55 +29015,55 @@
         <v>1</v>
       </c>
       <c r="M422" s="0">
-        <v>1.6499999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="N422" s="0">
-        <v>1.7</v>
-      </c>
-      <c r="O422" s="0"/>
+        <v>0.81000000000000005</v>
+      </c>
+      <c r="O422" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P422" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q422" s="0"/>
       <c r="R422" s="0">
-        <v>915.39999999999998</v>
+        <v>847.01999999999998</v>
       </c>
       <c r="S422" s="0"/>
       <c r="T422" s="0"/>
       <c r="U422" s="0"/>
       <c r="V422" s="0"/>
-      <c r="W422" s="0"/>
+      <c r="W422" s="0" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B423" s="1">
-        <v>45873.397743055553</v>
-      </c>
-      <c r="C423" s="0">
-        <v>83.597814</v>
-      </c>
-      <c r="D423" s="0">
-        <v>-12.444196</v>
-      </c>
+        <v>45886</v>
+      </c>
+      <c r="C423" s="0"/>
+      <c r="D423" s="0"/>
       <c r="E423" s="0">
-        <v>1.72</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F423" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G423" s="0">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="H423" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I423" s="0">
         <v>3</v>
       </c>
       <c r="J423" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K423" s="0" t="s">
         <v>18</v>
@@ -29010,42 +29072,46 @@
         <v>1</v>
       </c>
       <c r="M423" s="0">
-        <v>1.7</v>
+        <v>0.81000000000000005</v>
       </c>
       <c r="N423" s="0">
-        <v>1.75</v>
-      </c>
-      <c r="O423" s="0"/>
+        <v>0.87</v>
+      </c>
+      <c r="O423" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P423" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q423" s="0"/>
       <c r="R423" s="0">
-        <v>913.44000000000005</v>
+        <v>854.74000000000001</v>
       </c>
       <c r="S423" s="0"/>
       <c r="T423" s="0"/>
       <c r="U423" s="0"/>
       <c r="V423" s="0"/>
-      <c r="W423" s="0"/>
+      <c r="W423" s="0" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B424" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C424" s="0"/>
       <c r="D424" s="0"/>
       <c r="E424" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F424" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G424" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H424" s="0">
         <v>22</v>
@@ -29054,7 +29120,7 @@
         <v>3</v>
       </c>
       <c r="J424" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K424" s="0" t="s">
         <v>18</v>
@@ -29063,44 +29129,46 @@
         <v>1</v>
       </c>
       <c r="M424" s="0">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="N424" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="O424" s="0"/>
+        <v>0.93000000000000005</v>
+      </c>
+      <c r="O424" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P424" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q424" s="0"/>
       <c r="R424" s="0">
-        <v>835</v>
+        <v>864.23000000000002</v>
       </c>
       <c r="S424" s="0"/>
       <c r="T424" s="0"/>
       <c r="U424" s="0"/>
       <c r="V424" s="0"/>
       <c r="W424" s="0" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B425" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C425" s="0"/>
       <c r="D425" s="0"/>
       <c r="E425" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F425" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G425" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H425" s="0">
         <v>22</v>
@@ -29109,7 +29177,7 @@
         <v>3</v>
       </c>
       <c r="J425" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K425" s="0" t="s">
         <v>18</v>
@@ -29118,44 +29186,46 @@
         <v>1</v>
       </c>
       <c r="M425" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.93000000000000005</v>
       </c>
       <c r="N425" s="0">
+        <v>0.98999999999999999</v>
+      </c>
+      <c r="O425" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O425" s="0"/>
       <c r="P425" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q425" s="0"/>
       <c r="R425" s="0">
-        <v>840.02999999999997</v>
+        <v>895.32000000000005</v>
       </c>
       <c r="S425" s="0"/>
       <c r="T425" s="0"/>
       <c r="U425" s="0"/>
       <c r="V425" s="0"/>
       <c r="W425" s="0" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B426" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C426" s="0"/>
       <c r="D426" s="0"/>
       <c r="E426" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F426" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G426" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H426" s="0">
         <v>22</v>
@@ -29164,7 +29234,7 @@
         <v>3</v>
       </c>
       <c r="J426" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K426" s="0" t="s">
         <v>18</v>
@@ -29173,44 +29243,46 @@
         <v>1</v>
       </c>
       <c r="M426" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="N426" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="O426" s="0"/>
+        <v>1.0800000000000001</v>
+      </c>
+      <c r="O426" s="0">
+        <v>0.13</v>
+      </c>
       <c r="P426" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q426" s="0"/>
       <c r="R426" s="0">
-        <v>836.58000000000004</v>
+        <v>895.13999999999999</v>
       </c>
       <c r="S426" s="0"/>
       <c r="T426" s="0"/>
       <c r="U426" s="0"/>
       <c r="V426" s="0"/>
       <c r="W426" s="0" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B427" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C427" s="0"/>
       <c r="D427" s="0"/>
       <c r="E427" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F427" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G427" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H427" s="0">
         <v>22</v>
@@ -29219,7 +29291,7 @@
         <v>3</v>
       </c>
       <c r="J427" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K427" s="0" t="s">
         <v>18</v>
@@ -29228,44 +29300,46 @@
         <v>1</v>
       </c>
       <c r="M427" s="0">
-        <v>0.14999999999999999</v>
+        <v>1.0800000000000001</v>
       </c>
       <c r="N427" s="0">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="O427" s="0"/>
+        <v>1.1500000000000001</v>
+      </c>
+      <c r="O427" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P427" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q427" s="0"/>
       <c r="R427" s="0">
-        <v>835</v>
+        <v>835.5</v>
       </c>
       <c r="S427" s="0"/>
       <c r="T427" s="0"/>
       <c r="U427" s="0"/>
       <c r="V427" s="0"/>
       <c r="W427" s="0" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B428" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C428" s="0"/>
       <c r="D428" s="0"/>
       <c r="E428" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F428" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G428" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H428" s="0">
         <v>22</v>
@@ -29274,7 +29348,7 @@
         <v>3</v>
       </c>
       <c r="J428" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K428" s="0" t="s">
         <v>18</v>
@@ -29283,44 +29357,46 @@
         <v>1</v>
       </c>
       <c r="M428" s="0">
-        <v>0.20999999999999999</v>
+        <v>1.1500000000000001</v>
       </c>
       <c r="N428" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="O428" s="0"/>
+        <v>1.1900000000000002</v>
+      </c>
+      <c r="O428" s="0">
+        <v>0.10000000000000001</v>
+      </c>
       <c r="P428" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q428" s="0"/>
       <c r="R428" s="0">
-        <v>835</v>
+        <v>882.35000000000002</v>
       </c>
       <c r="S428" s="0"/>
       <c r="T428" s="0"/>
       <c r="U428" s="0"/>
       <c r="V428" s="0"/>
       <c r="W428" s="0" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B429" s="1">
-        <v>45874</v>
+        <v>45886</v>
       </c>
       <c r="C429" s="0"/>
       <c r="D429" s="0"/>
       <c r="E429" s="0">
-        <v>1.3200000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="F429" s="0">
-        <v>1.46</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="G429" s="0">
-        <v>1.325</v>
+        <v>1.24</v>
       </c>
       <c r="H429" s="0">
         <v>22</v>
@@ -29329,7 +29405,7 @@
         <v>3</v>
       </c>
       <c r="J429" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K429" s="0" t="s">
         <v>18</v>
@@ -29338,1941 +29414,26 @@
         <v>1</v>
       </c>
       <c r="M429" s="0">
-        <v>0.25</v>
+        <v>1.1900000000000002</v>
       </c>
       <c r="N429" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="O429" s="0"/>
+        <v>1.2400000000000002</v>
+      </c>
+      <c r="O429" s="0">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="P429" s="0">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q429" s="0"/>
       <c r="R429" s="0">
-        <v>848.88999999999999</v>
+        <v>873.72000000000003</v>
       </c>
       <c r="S429" s="0"/>
       <c r="T429" s="0"/>
       <c r="U429" s="0"/>
       <c r="V429" s="0"/>
       <c r="W429" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B430" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C430" s="0"/>
-      <c r="D430" s="0"/>
-      <c r="E430" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F430" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G430" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H430" s="0">
-        <v>22</v>
-      </c>
-      <c r="I430" s="0">
-        <v>3</v>
-      </c>
-      <c r="J430" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K430" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L430" s="0">
-        <v>1</v>
-      </c>
-      <c r="M430" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="N430" s="0">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="O430" s="0"/>
-      <c r="P430" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q430" s="0"/>
-      <c r="R430" s="0">
-        <v>883.69000000000005</v>
-      </c>
-      <c r="S430" s="0"/>
-      <c r="T430" s="0"/>
-      <c r="U430" s="0"/>
-      <c r="V430" s="0"/>
-      <c r="W430" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B431" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C431" s="0"/>
-      <c r="D431" s="0"/>
-      <c r="E431" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F431" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G431" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H431" s="0">
-        <v>22</v>
-      </c>
-      <c r="I431" s="0">
-        <v>3</v>
-      </c>
-      <c r="J431" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K431" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L431" s="0">
-        <v>1</v>
-      </c>
-      <c r="M431" s="0">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="N431" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="O431" s="0"/>
-      <c r="P431" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q431" s="0"/>
-      <c r="R431" s="0">
-        <v>868.80999999999995</v>
-      </c>
-      <c r="S431" s="0"/>
-      <c r="T431" s="0"/>
-      <c r="U431" s="0"/>
-      <c r="V431" s="0"/>
-      <c r="W431" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B432" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C432" s="0"/>
-      <c r="D432" s="0"/>
-      <c r="E432" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F432" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G432" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H432" s="0">
-        <v>22</v>
-      </c>
-      <c r="I432" s="0">
-        <v>3</v>
-      </c>
-      <c r="J432" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K432" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L432" s="0">
-        <v>1</v>
-      </c>
-      <c r="M432" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="N432" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="O432" s="0"/>
-      <c r="P432" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q432" s="0"/>
-      <c r="R432" s="0">
-        <v>888.38999999999999</v>
-      </c>
-      <c r="S432" s="0"/>
-      <c r="T432" s="0"/>
-      <c r="U432" s="0"/>
-      <c r="V432" s="0"/>
-      <c r="W432" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B433" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C433" s="0"/>
-      <c r="D433" s="0"/>
-      <c r="E433" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F433" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G433" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H433" s="0">
-        <v>22</v>
-      </c>
-      <c r="I433" s="0">
-        <v>3</v>
-      </c>
-      <c r="J433" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K433" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L433" s="0">
-        <v>1</v>
-      </c>
-      <c r="M433" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="N433" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="O433" s="0"/>
-      <c r="P433" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q433" s="0"/>
-      <c r="R433" s="0">
-        <v>907.75999999999999</v>
-      </c>
-      <c r="S433" s="0"/>
-      <c r="T433" s="0"/>
-      <c r="U433" s="0"/>
-      <c r="V433" s="0"/>
-      <c r="W433" s="0" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B434" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C434" s="0"/>
-      <c r="D434" s="0"/>
-      <c r="E434" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F434" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G434" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H434" s="0">
-        <v>22</v>
-      </c>
-      <c r="I434" s="0">
-        <v>3</v>
-      </c>
-      <c r="J434" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K434" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L434" s="0">
-        <v>1</v>
-      </c>
-      <c r="M434" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="N434" s="0">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O434" s="0"/>
-      <c r="P434" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q434" s="0"/>
-      <c r="R434" s="0">
-        <v>879.98000000000002</v>
-      </c>
-      <c r="S434" s="0"/>
-      <c r="T434" s="0"/>
-      <c r="U434" s="0"/>
-      <c r="V434" s="0"/>
-      <c r="W434" s="0" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B435" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C435" s="0"/>
-      <c r="D435" s="0"/>
-      <c r="E435" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F435" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G435" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H435" s="0">
-        <v>22</v>
-      </c>
-      <c r="I435" s="0">
-        <v>3</v>
-      </c>
-      <c r="J435" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K435" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L435" s="0">
-        <v>1</v>
-      </c>
-      <c r="M435" s="0">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N435" s="0">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="O435" s="0"/>
-      <c r="P435" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q435" s="0"/>
-      <c r="R435" s="0">
-        <v>877.13</v>
-      </c>
-      <c r="S435" s="0"/>
-      <c r="T435" s="0"/>
-      <c r="U435" s="0"/>
-      <c r="V435" s="0"/>
-      <c r="W435" s="0" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B436" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C436" s="0"/>
-      <c r="D436" s="0"/>
-      <c r="E436" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F436" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G436" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H436" s="0">
-        <v>22</v>
-      </c>
-      <c r="I436" s="0">
-        <v>3</v>
-      </c>
-      <c r="J436" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K436" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L436" s="0">
-        <v>1</v>
-      </c>
-      <c r="M436" s="0">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="N436" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="O436" s="0"/>
-      <c r="P436" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q436" s="0"/>
-      <c r="R436" s="0">
-        <v>909.88999999999999</v>
-      </c>
-      <c r="S436" s="0"/>
-      <c r="T436" s="0"/>
-      <c r="U436" s="0"/>
-      <c r="V436" s="0"/>
-      <c r="W436" s="0" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B437" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C437" s="0"/>
-      <c r="D437" s="0"/>
-      <c r="E437" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F437" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G437" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H437" s="0">
-        <v>22</v>
-      </c>
-      <c r="I437" s="0">
-        <v>3</v>
-      </c>
-      <c r="J437" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K437" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L437" s="0">
-        <v>1</v>
-      </c>
-      <c r="M437" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="N437" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="O437" s="0"/>
-      <c r="P437" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q437" s="0"/>
-      <c r="R437" s="0">
-        <v>919.49000000000001</v>
-      </c>
-      <c r="S437" s="0"/>
-      <c r="T437" s="0"/>
-      <c r="U437" s="0"/>
-      <c r="V437" s="0"/>
-      <c r="W437" s="0" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B438" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C438" s="0"/>
-      <c r="D438" s="0"/>
-      <c r="E438" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F438" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G438" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H438" s="0">
-        <v>22</v>
-      </c>
-      <c r="I438" s="0">
-        <v>3</v>
-      </c>
-      <c r="J438" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K438" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L438" s="0">
-        <v>1</v>
-      </c>
-      <c r="M438" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="N438" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="O438" s="0"/>
-      <c r="P438" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q438" s="0"/>
-      <c r="R438" s="0">
-        <v>883.77999999999997</v>
-      </c>
-      <c r="S438" s="0"/>
-      <c r="T438" s="0"/>
-      <c r="U438" s="0"/>
-      <c r="V438" s="0"/>
-      <c r="W438" s="0" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B439" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C439" s="0"/>
-      <c r="D439" s="0"/>
-      <c r="E439" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F439" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G439" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H439" s="0">
-        <v>22</v>
-      </c>
-      <c r="I439" s="0">
-        <v>3</v>
-      </c>
-      <c r="J439" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K439" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L439" s="0">
-        <v>1</v>
-      </c>
-      <c r="M439" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="N439" s="0">
-        <v>1</v>
-      </c>
-      <c r="O439" s="0"/>
-      <c r="P439" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q439" s="0"/>
-      <c r="R439" s="0">
-        <v>893.38999999999999</v>
-      </c>
-      <c r="S439" s="0"/>
-      <c r="T439" s="0"/>
-      <c r="U439" s="0"/>
-      <c r="V439" s="0"/>
-      <c r="W439" s="0" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B440" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C440" s="0"/>
-      <c r="D440" s="0"/>
-      <c r="E440" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F440" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G440" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H440" s="0">
-        <v>22</v>
-      </c>
-      <c r="I440" s="0">
-        <v>3</v>
-      </c>
-      <c r="J440" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K440" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L440" s="0">
-        <v>1</v>
-      </c>
-      <c r="M440" s="0">
-        <v>1</v>
-      </c>
-      <c r="N440" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="O440" s="0"/>
-      <c r="P440" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q440" s="0"/>
-      <c r="R440" s="0">
-        <v>900.75999999999999</v>
-      </c>
-      <c r="S440" s="0"/>
-      <c r="T440" s="0"/>
-      <c r="U440" s="0"/>
-      <c r="V440" s="0"/>
-      <c r="W440" s="0"/>
-    </row>
-    <row r="441">
-      <c r="A441" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B441" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C441" s="0"/>
-      <c r="D441" s="0"/>
-      <c r="E441" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F441" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G441" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H441" s="0">
-        <v>22</v>
-      </c>
-      <c r="I441" s="0">
-        <v>3</v>
-      </c>
-      <c r="J441" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K441" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L441" s="0">
-        <v>1</v>
-      </c>
-      <c r="M441" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N441" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="O441" s="0"/>
-      <c r="P441" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q441" s="0"/>
-      <c r="R441" s="0">
-        <v>919.61000000000001</v>
-      </c>
-      <c r="S441" s="0"/>
-      <c r="T441" s="0"/>
-      <c r="U441" s="0"/>
-      <c r="V441" s="0"/>
-      <c r="W441" s="0"/>
-    </row>
-    <row r="442">
-      <c r="A442" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B442" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C442" s="0"/>
-      <c r="D442" s="0"/>
-      <c r="E442" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F442" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G442" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H442" s="0">
-        <v>22</v>
-      </c>
-      <c r="I442" s="0">
-        <v>3</v>
-      </c>
-      <c r="J442" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K442" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L442" s="0">
-        <v>1</v>
-      </c>
-      <c r="M442" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="N442" s="0">
-        <v>1.26</v>
-      </c>
-      <c r="O442" s="0"/>
-      <c r="P442" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q442" s="0"/>
-      <c r="R442" s="0">
-        <v>921.37</v>
-      </c>
-      <c r="S442" s="0"/>
-      <c r="T442" s="0"/>
-      <c r="U442" s="0"/>
-      <c r="V442" s="0"/>
-      <c r="W442" s="0"/>
-    </row>
-    <row r="443">
-      <c r="A443" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B443" s="1">
-        <v>45874</v>
-      </c>
-      <c r="C443" s="0"/>
-      <c r="D443" s="0"/>
-      <c r="E443" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="F443" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="G443" s="0">
-        <v>1.325</v>
-      </c>
-      <c r="H443" s="0">
-        <v>22</v>
-      </c>
-      <c r="I443" s="0">
-        <v>3</v>
-      </c>
-      <c r="J443" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="K443" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L443" s="0">
-        <v>1</v>
-      </c>
-      <c r="M443" s="0">
-        <v>1.26</v>
-      </c>
-      <c r="N443" s="0">
-        <v>1.3200000000000001</v>
-      </c>
-      <c r="O443" s="0"/>
-      <c r="P443" s="0">
-        <v>-22</v>
-      </c>
-      <c r="Q443" s="0"/>
-      <c r="R443" s="0">
-        <v>918</v>
-      </c>
-      <c r="S443" s="0"/>
-      <c r="T443" s="0"/>
-      <c r="U443" s="0"/>
-      <c r="V443" s="0"/>
-      <c r="W443" s="0"/>
-    </row>
-    <row r="444">
-      <c r="A444" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B444" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C444" s="0"/>
-      <c r="D444" s="0"/>
-      <c r="E444" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F444" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G444" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H444" s="0">
-        <v>23</v>
-      </c>
-      <c r="I444" s="0">
-        <v>3</v>
-      </c>
-      <c r="J444" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K444" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L444" s="0">
-        <v>1</v>
-      </c>
-      <c r="M444" s="0">
-        <v>0</v>
-      </c>
-      <c r="N444" s="0">
-        <v>0.059999999999999998</v>
-      </c>
-      <c r="O444" s="0"/>
-      <c r="P444" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q444" s="0"/>
-      <c r="R444" s="0">
-        <v>879.48000000000002</v>
-      </c>
-      <c r="S444" s="0"/>
-      <c r="T444" s="0"/>
-      <c r="U444" s="0"/>
-      <c r="V444" s="0"/>
-      <c r="W444" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B445" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C445" s="0"/>
-      <c r="D445" s="0"/>
-      <c r="E445" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F445" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G445" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H445" s="0">
-        <v>23</v>
-      </c>
-      <c r="I445" s="0">
-        <v>3</v>
-      </c>
-      <c r="J445" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K445" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L445" s="0">
-        <v>1</v>
-      </c>
-      <c r="M445" s="0">
-        <v>0.059999999999999998</v>
-      </c>
-      <c r="N445" s="0">
-        <v>0.12</v>
-      </c>
-      <c r="O445" s="0"/>
-      <c r="P445" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q445" s="0"/>
-      <c r="R445" s="0">
-        <v>869.49000000000001</v>
-      </c>
-      <c r="S445" s="0"/>
-      <c r="T445" s="0"/>
-      <c r="U445" s="0"/>
-      <c r="V445" s="0"/>
-      <c r="W445" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B446" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C446" s="0"/>
-      <c r="D446" s="0"/>
-      <c r="E446" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F446" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G446" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H446" s="0">
-        <v>23</v>
-      </c>
-      <c r="I446" s="0">
-        <v>3</v>
-      </c>
-      <c r="J446" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K446" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L446" s="0">
-        <v>1</v>
-      </c>
-      <c r="M446" s="0">
-        <v>0.12</v>
-      </c>
-      <c r="N446" s="0">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="O446" s="0"/>
-      <c r="P446" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q446" s="0"/>
-      <c r="R446" s="0">
-        <v>841.63999999999999</v>
-      </c>
-      <c r="S446" s="0"/>
-      <c r="T446" s="0"/>
-      <c r="U446" s="0"/>
-      <c r="V446" s="0"/>
-      <c r="W446" s="0" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B447" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C447" s="0"/>
-      <c r="D447" s="0"/>
-      <c r="E447" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F447" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G447" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H447" s="0">
-        <v>23</v>
-      </c>
-      <c r="I447" s="0">
-        <v>3</v>
-      </c>
-      <c r="J447" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K447" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L447" s="0">
-        <v>1</v>
-      </c>
-      <c r="M447" s="0">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="N447" s="0">
-        <v>0.22</v>
-      </c>
-      <c r="O447" s="0"/>
-      <c r="P447" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q447" s="0"/>
-      <c r="R447" s="0">
-        <v>839.62</v>
-      </c>
-      <c r="S447" s="0"/>
-      <c r="T447" s="0"/>
-      <c r="U447" s="0"/>
-      <c r="V447" s="0"/>
-      <c r="W447" s="0" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B448" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C448" s="0"/>
-      <c r="D448" s="0"/>
-      <c r="E448" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F448" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G448" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H448" s="0">
-        <v>23</v>
-      </c>
-      <c r="I448" s="0">
-        <v>3</v>
-      </c>
-      <c r="J448" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K448" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L448" s="0">
-        <v>1</v>
-      </c>
-      <c r="M448" s="0">
-        <v>0.22</v>
-      </c>
-      <c r="N448" s="0">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="O448" s="0"/>
-      <c r="P448" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q448" s="0"/>
-      <c r="R448" s="0">
-        <v>835.5</v>
-      </c>
-      <c r="S448" s="0"/>
-      <c r="T448" s="0"/>
-      <c r="U448" s="0"/>
-      <c r="V448" s="0"/>
-      <c r="W448" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B449" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C449" s="0"/>
-      <c r="D449" s="0"/>
-      <c r="E449" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F449" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G449" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H449" s="0">
-        <v>23</v>
-      </c>
-      <c r="I449" s="0">
-        <v>3</v>
-      </c>
-      <c r="J449" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K449" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L449" s="0">
-        <v>1</v>
-      </c>
-      <c r="M449" s="0">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="N449" s="0">
-        <v>0.33000000000000002</v>
-      </c>
-      <c r="O449" s="0"/>
-      <c r="P449" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q449" s="0"/>
-      <c r="R449" s="0">
-        <v>835.5</v>
-      </c>
-      <c r="S449" s="0"/>
-      <c r="T449" s="0"/>
-      <c r="U449" s="0"/>
-      <c r="V449" s="0"/>
-      <c r="W449" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B450" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C450" s="0"/>
-      <c r="D450" s="0"/>
-      <c r="E450" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F450" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G450" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H450" s="0">
-        <v>23</v>
-      </c>
-      <c r="I450" s="0">
-        <v>3</v>
-      </c>
-      <c r="J450" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K450" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L450" s="0">
-        <v>1</v>
-      </c>
-      <c r="M450" s="0">
-        <v>0.33000000000000002</v>
-      </c>
-      <c r="N450" s="0">
-        <v>0.39000000000000001</v>
-      </c>
-      <c r="O450" s="0"/>
-      <c r="P450" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q450" s="0"/>
-      <c r="R450" s="0">
-        <v>835.5</v>
-      </c>
-      <c r="S450" s="0"/>
-      <c r="T450" s="0"/>
-      <c r="U450" s="0"/>
-      <c r="V450" s="0"/>
-      <c r="W450" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B451" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C451" s="0"/>
-      <c r="D451" s="0"/>
-      <c r="E451" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F451" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G451" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H451" s="0">
-        <v>23</v>
-      </c>
-      <c r="I451" s="0">
-        <v>3</v>
-      </c>
-      <c r="J451" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K451" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L451" s="0">
-        <v>1</v>
-      </c>
-      <c r="M451" s="0">
-        <v>0.39000000000000001</v>
-      </c>
-      <c r="N451" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="O451" s="0"/>
-      <c r="P451" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q451" s="0"/>
-      <c r="R451" s="0">
-        <v>841.88</v>
-      </c>
-      <c r="S451" s="0"/>
-      <c r="T451" s="0"/>
-      <c r="U451" s="0"/>
-      <c r="V451" s="0"/>
-      <c r="W451" s="0" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B452" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C452" s="0"/>
-      <c r="D452" s="0"/>
-      <c r="E452" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F452" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G452" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H452" s="0">
-        <v>23</v>
-      </c>
-      <c r="I452" s="0">
-        <v>3</v>
-      </c>
-      <c r="J452" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K452" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L452" s="0">
-        <v>1</v>
-      </c>
-      <c r="M452" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="N452" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="O452" s="0"/>
-      <c r="P452" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q452" s="0"/>
-      <c r="R452" s="0">
-        <v>835.5</v>
-      </c>
-      <c r="S452" s="0"/>
-      <c r="T452" s="0"/>
-      <c r="U452" s="0"/>
-      <c r="V452" s="0"/>
-      <c r="W452" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B453" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C453" s="0"/>
-      <c r="D453" s="0"/>
-      <c r="E453" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F453" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G453" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H453" s="0">
-        <v>23</v>
-      </c>
-      <c r="I453" s="0">
-        <v>3</v>
-      </c>
-      <c r="J453" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K453" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L453" s="0">
-        <v>1</v>
-      </c>
-      <c r="M453" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="N453" s="0">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O453" s="0"/>
-      <c r="P453" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q453" s="0"/>
-      <c r="R453" s="0">
-        <v>840.57000000000005</v>
-      </c>
-      <c r="S453" s="0"/>
-      <c r="T453" s="0"/>
-      <c r="U453" s="0"/>
-      <c r="V453" s="0"/>
-      <c r="W453" s="0" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B454" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C454" s="0"/>
-      <c r="D454" s="0"/>
-      <c r="E454" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F454" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G454" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H454" s="0">
-        <v>23</v>
-      </c>
-      <c r="I454" s="0">
-        <v>3</v>
-      </c>
-      <c r="J454" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K454" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L454" s="0">
-        <v>1</v>
-      </c>
-      <c r="M454" s="0">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N454" s="0">
-        <v>0.63</v>
-      </c>
-      <c r="O454" s="0"/>
-      <c r="P454" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q454" s="0"/>
-      <c r="R454" s="0">
-        <v>847.29999999999995</v>
-      </c>
-      <c r="S454" s="0"/>
-      <c r="T454" s="0"/>
-      <c r="U454" s="0"/>
-      <c r="V454" s="0"/>
-      <c r="W454" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B455" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C455" s="0"/>
-      <c r="D455" s="0"/>
-      <c r="E455" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F455" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G455" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H455" s="0">
-        <v>23</v>
-      </c>
-      <c r="I455" s="0">
-        <v>3</v>
-      </c>
-      <c r="J455" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K455" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L455" s="0">
-        <v>1</v>
-      </c>
-      <c r="M455" s="0">
-        <v>0.63</v>
-      </c>
-      <c r="N455" s="0">
-        <v>0.68999999999999995</v>
-      </c>
-      <c r="O455" s="0"/>
-      <c r="P455" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q455" s="0"/>
-      <c r="R455" s="0">
-        <v>849.52999999999997</v>
-      </c>
-      <c r="S455" s="0"/>
-      <c r="T455" s="0"/>
-      <c r="U455" s="0"/>
-      <c r="V455" s="0"/>
-      <c r="W455" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B456" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C456" s="0"/>
-      <c r="D456" s="0"/>
-      <c r="E456" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F456" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G456" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H456" s="0">
-        <v>23</v>
-      </c>
-      <c r="I456" s="0">
-        <v>3</v>
-      </c>
-      <c r="J456" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K456" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L456" s="0">
-        <v>1</v>
-      </c>
-      <c r="M456" s="0">
-        <v>0.68999999999999995</v>
-      </c>
-      <c r="N456" s="0">
-        <v>0.75</v>
-      </c>
-      <c r="O456" s="0"/>
-      <c r="P456" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q456" s="0"/>
-      <c r="R456" s="0">
-        <v>841.91999999999996</v>
-      </c>
-      <c r="S456" s="0"/>
-      <c r="T456" s="0"/>
-      <c r="U456" s="0"/>
-      <c r="V456" s="0"/>
-      <c r="W456" s="0" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B457" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C457" s="0"/>
-      <c r="D457" s="0"/>
-      <c r="E457" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F457" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G457" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H457" s="0">
-        <v>23</v>
-      </c>
-      <c r="I457" s="0">
-        <v>3</v>
-      </c>
-      <c r="J457" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K457" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L457" s="0">
-        <v>1</v>
-      </c>
-      <c r="M457" s="0">
-        <v>0.75</v>
-      </c>
-      <c r="N457" s="0">
-        <v>0.81000000000000005</v>
-      </c>
-      <c r="O457" s="0"/>
-      <c r="P457" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q457" s="0"/>
-      <c r="R457" s="0">
-        <v>847.01999999999998</v>
-      </c>
-      <c r="S457" s="0"/>
-      <c r="T457" s="0"/>
-      <c r="U457" s="0"/>
-      <c r="V457" s="0"/>
-      <c r="W457" s="0" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B458" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C458" s="0"/>
-      <c r="D458" s="0"/>
-      <c r="E458" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F458" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G458" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H458" s="0">
-        <v>23</v>
-      </c>
-      <c r="I458" s="0">
-        <v>3</v>
-      </c>
-      <c r="J458" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K458" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L458" s="0">
-        <v>1</v>
-      </c>
-      <c r="M458" s="0">
-        <v>0.81000000000000005</v>
-      </c>
-      <c r="N458" s="0">
-        <v>0.87</v>
-      </c>
-      <c r="O458" s="0"/>
-      <c r="P458" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q458" s="0"/>
-      <c r="R458" s="0">
-        <v>854.74000000000001</v>
-      </c>
-      <c r="S458" s="0"/>
-      <c r="T458" s="0"/>
-      <c r="U458" s="0"/>
-      <c r="V458" s="0"/>
-      <c r="W458" s="0" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B459" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C459" s="0"/>
-      <c r="D459" s="0"/>
-      <c r="E459" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F459" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G459" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H459" s="0">
-        <v>23</v>
-      </c>
-      <c r="I459" s="0">
-        <v>3</v>
-      </c>
-      <c r="J459" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K459" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L459" s="0">
-        <v>1</v>
-      </c>
-      <c r="M459" s="0">
-        <v>0.87</v>
-      </c>
-      <c r="N459" s="0">
-        <v>0.93000000000000005</v>
-      </c>
-      <c r="O459" s="0"/>
-      <c r="P459" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q459" s="0"/>
-      <c r="R459" s="0">
-        <v>864.23000000000002</v>
-      </c>
-      <c r="S459" s="0"/>
-      <c r="T459" s="0"/>
-      <c r="U459" s="0"/>
-      <c r="V459" s="0"/>
-      <c r="W459" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B460" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C460" s="0"/>
-      <c r="D460" s="0"/>
-      <c r="E460" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F460" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G460" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H460" s="0">
-        <v>23</v>
-      </c>
-      <c r="I460" s="0">
-        <v>3</v>
-      </c>
-      <c r="J460" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K460" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L460" s="0">
-        <v>1</v>
-      </c>
-      <c r="M460" s="0">
-        <v>0.93000000000000005</v>
-      </c>
-      <c r="N460" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="O460" s="0"/>
-      <c r="P460" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q460" s="0"/>
-      <c r="R460" s="0">
-        <v>895.32000000000005</v>
-      </c>
-      <c r="S460" s="0"/>
-      <c r="T460" s="0"/>
-      <c r="U460" s="0"/>
-      <c r="V460" s="0"/>
-      <c r="W460" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B461" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C461" s="0"/>
-      <c r="D461" s="0"/>
-      <c r="E461" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F461" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G461" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H461" s="0">
-        <v>23</v>
-      </c>
-      <c r="I461" s="0">
-        <v>3</v>
-      </c>
-      <c r="J461" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K461" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L461" s="0">
-        <v>1</v>
-      </c>
-      <c r="M461" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="N461" s="0">
-        <v>1.0800000000000001</v>
-      </c>
-      <c r="O461" s="0"/>
-      <c r="P461" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q461" s="0"/>
-      <c r="R461" s="0">
-        <v>895.13999999999999</v>
-      </c>
-      <c r="S461" s="0"/>
-      <c r="T461" s="0"/>
-      <c r="U461" s="0"/>
-      <c r="V461" s="0"/>
-      <c r="W461" s="0" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B462" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C462" s="0"/>
-      <c r="D462" s="0"/>
-      <c r="E462" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F462" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G462" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H462" s="0">
-        <v>23</v>
-      </c>
-      <c r="I462" s="0">
-        <v>3</v>
-      </c>
-      <c r="J462" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K462" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L462" s="0">
-        <v>1</v>
-      </c>
-      <c r="M462" s="0">
-        <v>1.0800000000000001</v>
-      </c>
-      <c r="N462" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-      <c r="O462" s="0"/>
-      <c r="P462" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q462" s="0"/>
-      <c r="R462" s="0">
-        <v>835.5</v>
-      </c>
-      <c r="S462" s="0"/>
-      <c r="T462" s="0"/>
-      <c r="U462" s="0"/>
-      <c r="V462" s="0"/>
-      <c r="W462" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B463" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C463" s="0"/>
-      <c r="D463" s="0"/>
-      <c r="E463" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F463" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G463" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H463" s="0">
-        <v>23</v>
-      </c>
-      <c r="I463" s="0">
-        <v>3</v>
-      </c>
-      <c r="J463" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K463" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L463" s="0">
-        <v>1</v>
-      </c>
-      <c r="M463" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-      <c r="N463" s="0">
-        <v>1.1900000000000002</v>
-      </c>
-      <c r="O463" s="0"/>
-      <c r="P463" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q463" s="0"/>
-      <c r="R463" s="0">
-        <v>882.35000000000002</v>
-      </c>
-      <c r="S463" s="0"/>
-      <c r="T463" s="0"/>
-      <c r="U463" s="0"/>
-      <c r="V463" s="0"/>
-      <c r="W463" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B464" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C464" s="0"/>
-      <c r="D464" s="0"/>
-      <c r="E464" s="0">
-        <v>1.3799999999999999</v>
-      </c>
-      <c r="F464" s="0">
-        <v>1.4399999999999999</v>
-      </c>
-      <c r="G464" s="0">
-        <v>1.24</v>
-      </c>
-      <c r="H464" s="0">
-        <v>23</v>
-      </c>
-      <c r="I464" s="0">
-        <v>3</v>
-      </c>
-      <c r="J464" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="K464" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L464" s="0">
-        <v>1</v>
-      </c>
-      <c r="M464" s="0">
-        <v>1.1900000000000002</v>
-      </c>
-      <c r="N464" s="0">
-        <v>1.2400000000000002</v>
-      </c>
-      <c r="O464" s="0"/>
-      <c r="P464" s="0">
-        <v>-23</v>
-      </c>
-      <c r="Q464" s="0"/>
-      <c r="R464" s="0">
-        <v>873.72000000000003</v>
-      </c>
-      <c r="S464" s="0"/>
-      <c r="T464" s="0"/>
-      <c r="U464" s="0"/>
-      <c r="V464" s="0"/>
-      <c r="W464" s="0" t="s">
         <v>61</v>
       </c>
     </row>

--- a/Export/Coring_data_export.xlsx
+++ b/Export/Coring_data_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="73184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95878" uniqueCount="184">
   <si>
     <t>Event label</t>
   </si>
@@ -5334,7 +5334,7 @@
         <v>174</v>
       </c>
       <c r="B68" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C68" s="0"/>
       <c r="D68" s="0"/>
@@ -5389,7 +5389,7 @@
         <v>174</v>
       </c>
       <c r="B69" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C69" s="0"/>
       <c r="D69" s="0"/>
@@ -5444,7 +5444,7 @@
         <v>174</v>
       </c>
       <c r="B70" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C70" s="0"/>
       <c r="D70" s="0"/>
@@ -5499,7 +5499,7 @@
         <v>174</v>
       </c>
       <c r="B71" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C71" s="0"/>
       <c r="D71" s="0"/>
@@ -5554,7 +5554,7 @@
         <v>174</v>
       </c>
       <c r="B72" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C72" s="0"/>
       <c r="D72" s="0"/>
@@ -5609,7 +5609,7 @@
         <v>174</v>
       </c>
       <c r="B73" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C73" s="0"/>
       <c r="D73" s="0"/>
@@ -5664,7 +5664,7 @@
         <v>174</v>
       </c>
       <c r="B74" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C74" s="0"/>
       <c r="D74" s="0"/>
@@ -5719,7 +5719,7 @@
         <v>174</v>
       </c>
       <c r="B75" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C75" s="0"/>
       <c r="D75" s="0"/>
@@ -5774,7 +5774,7 @@
         <v>174</v>
       </c>
       <c r="B76" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C76" s="0"/>
       <c r="D76" s="0"/>
@@ -5831,7 +5831,7 @@
         <v>174</v>
       </c>
       <c r="B77" s="1">
-        <v>45865</v>
+        <v>45865.711805555555</v>
       </c>
       <c r="C77" s="0"/>
       <c r="D77" s="0"/>
@@ -14496,7 +14496,9 @@
       <c r="N202" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O202" s="0"/>
+      <c r="O202" s="0">
+        <v>1.5</v>
+      </c>
       <c r="P202" s="0">
         <v>-21</v>
       </c>
@@ -14506,13 +14508,17 @@
       <c r="R202" s="0">
         <v>877.99000000000001</v>
       </c>
-      <c r="S202" s="0"/>
-      <c r="T202" s="0"/>
+      <c r="S202" s="0">
+        <v>875.23000000000002</v>
+      </c>
+      <c r="T202" s="0">
+        <v>0.17999999999999999</v>
+      </c>
       <c r="U202" s="0">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="V202" s="0">
-        <v>0</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="W202" s="0" t="s">
         <v>101</v>
@@ -14561,7 +14567,9 @@
       <c r="N203" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O203" s="0"/>
+      <c r="O203" s="0">
+        <v>1</v>
+      </c>
       <c r="P203" s="0">
         <v>-21</v>
       </c>
@@ -14571,13 +14579,17 @@
       <c r="R203" s="0">
         <v>835.88</v>
       </c>
-      <c r="S203" s="0"/>
-      <c r="T203" s="0"/>
+      <c r="S203" s="0">
+        <v>833.25</v>
+      </c>
+      <c r="T203" s="0">
+        <v>0.11</v>
+      </c>
       <c r="U203" s="0">
-        <v>0</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="V203" s="0">
-        <v>0</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="W203" s="0" t="s">
         <v>102</v>
@@ -14627,7 +14639,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O204" s="0">
-        <v>1.5</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="P204" s="0">
         <v>-21</v>
@@ -14642,13 +14654,13 @@
         <v>871.53999999999996</v>
       </c>
       <c r="T204" s="0">
-        <v>0.22</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="U204" s="0">
         <v>0.050000000000000003</v>
       </c>
       <c r="V204" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="W204" s="0" t="s">
         <v>103</v>
@@ -14698,7 +14710,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="O205" s="0">
-        <v>1</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="P205" s="0">
         <v>-21</v>
@@ -14713,13 +14725,13 @@
         <v>858.14999999999998</v>
       </c>
       <c r="T205" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="U205" s="0">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="V205" s="0">
         <v>0.070000000000000007</v>
-      </c>
-      <c r="V205" s="0">
-        <v>0.080000000000000002</v>
       </c>
       <c r="W205" s="0" t="s">
         <v>103</v>
@@ -14769,7 +14781,7 @@
         <v>0.25</v>
       </c>
       <c r="O206" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="P206" s="0">
         <v>-21</v>
@@ -14784,13 +14796,13 @@
         <v>863.87</v>
       </c>
       <c r="T206" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U206" s="0">
         <v>0.059999999999999998</v>
       </c>
       <c r="V206" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="W206" s="0" t="s">
         <v>104</v>
@@ -14840,7 +14852,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O207" s="0">
-        <v>0.29999999999999999</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="P207" s="0">
         <v>-21</v>
@@ -14855,7 +14867,7 @@
         <v>884.75</v>
       </c>
       <c r="T207" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U207" s="0">
         <v>0.040000000000000001</v>
@@ -14911,7 +14923,7 @@
         <v>0.34000000000000002</v>
       </c>
       <c r="O208" s="0">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P208" s="0">
         <v>-21</v>
@@ -14926,7 +14938,7 @@
         <v>849.72000000000003</v>
       </c>
       <c r="T208" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.12</v>
       </c>
       <c r="U208" s="0">
         <v>0.070000000000000007</v>
@@ -14982,7 +14994,7 @@
         <v>0.39000000000000001</v>
       </c>
       <c r="O209" s="0">
-        <v>0.59999999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="P209" s="0">
         <v>-21</v>
@@ -14997,7 +15009,7 @@
         <v>861.69000000000005</v>
       </c>
       <c r="T209" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U209" s="0">
         <v>0.059999999999999998</v>
@@ -15053,7 +15065,7 @@
         <v>0.44</v>
       </c>
       <c r="O210" s="0">
-        <v>1.1000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="P210" s="0">
         <v>-21</v>
@@ -15068,13 +15080,13 @@
         <v>895.66999999999996</v>
       </c>
       <c r="T210" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.12</v>
       </c>
       <c r="U210" s="0">
-        <v>0.02</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="V210" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="W210" s="0" t="s">
         <v>107</v>
@@ -15124,7 +15136,7 @@
         <v>0.48999999999999999</v>
       </c>
       <c r="O211" s="0">
-        <v>1.3</v>
+        <v>1.8999999999999999</v>
       </c>
       <c r="P211" s="0">
         <v>-21</v>
@@ -15139,13 +15151,13 @@
         <v>885.97000000000003</v>
       </c>
       <c r="T211" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.11</v>
       </c>
       <c r="U211" s="0">
         <v>0.040000000000000001</v>
       </c>
       <c r="V211" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="W211" s="0" t="s">
         <v>108</v>
@@ -15195,7 +15207,7 @@
         <v>0.54000000000000004</v>
       </c>
       <c r="O212" s="0">
-        <v>1.7</v>
+        <v>2.6000000000000001</v>
       </c>
       <c r="P212" s="0">
         <v>-21</v>
@@ -15210,10 +15222,10 @@
         <v>877.97000000000003</v>
       </c>
       <c r="T212" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U212" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="V212" s="0">
         <v>0.050000000000000003</v>
@@ -15266,7 +15278,7 @@
         <v>0.58999999999999997</v>
       </c>
       <c r="O213" s="0">
-        <v>1.8999999999999999</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="P213" s="0">
         <v>-21</v>
@@ -15281,10 +15293,10 @@
         <v>896.17999999999995</v>
       </c>
       <c r="T213" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U213" s="0">
-        <v>0.02</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="V213" s="0">
         <v>0.029999999999999999</v>
@@ -15337,7 +15349,7 @@
         <v>0.65000000000000002</v>
       </c>
       <c r="O214" s="0">
-        <v>2.6000000000000001</v>
+        <v>2.8999999999999999</v>
       </c>
       <c r="P214" s="0">
         <v>-21</v>
@@ -15352,7 +15364,7 @@
         <v>892.64999999999998</v>
       </c>
       <c r="T214" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U214" s="0">
         <v>0.029999999999999999</v>
@@ -15408,7 +15420,7 @@
         <v>0.70999999999999996</v>
       </c>
       <c r="O215" s="0">
-        <v>2.7999999999999998</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="P215" s="0">
         <v>-21</v>
@@ -15423,7 +15435,7 @@
         <v>888.89999999999998</v>
       </c>
       <c r="T215" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="U215" s="0">
         <v>0.029999999999999999</v>
@@ -25423,7 +25435,7 @@
         <v>177</v>
       </c>
       <c r="B359" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C359" s="0"/>
       <c r="D359" s="0"/>
@@ -25478,7 +25490,7 @@
         <v>177</v>
       </c>
       <c r="B360" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C360" s="0"/>
       <c r="D360" s="0"/>
@@ -25533,7 +25545,7 @@
         <v>177</v>
       </c>
       <c r="B361" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C361" s="0"/>
       <c r="D361" s="0"/>
@@ -25586,7 +25598,7 @@
         <v>177</v>
       </c>
       <c r="B362" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C362" s="0"/>
       <c r="D362" s="0"/>
@@ -25641,7 +25653,7 @@
         <v>177</v>
       </c>
       <c r="B363" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C363" s="0"/>
       <c r="D363" s="0"/>
@@ -25696,7 +25708,7 @@
         <v>177</v>
       </c>
       <c r="B364" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C364" s="0"/>
       <c r="D364" s="0"/>
@@ -25749,7 +25761,7 @@
         <v>177</v>
       </c>
       <c r="B365" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C365" s="0"/>
       <c r="D365" s="0"/>
@@ -25806,7 +25818,7 @@
         <v>177</v>
       </c>
       <c r="B366" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C366" s="0"/>
       <c r="D366" s="0"/>
@@ -25863,7 +25875,7 @@
         <v>177</v>
       </c>
       <c r="B367" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C367" s="0"/>
       <c r="D367" s="0"/>
@@ -25918,7 +25930,7 @@
         <v>177</v>
       </c>
       <c r="B368" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C368" s="0"/>
       <c r="D368" s="0"/>
@@ -25975,7 +25987,7 @@
         <v>177</v>
       </c>
       <c r="B369" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C369" s="0"/>
       <c r="D369" s="0"/>
@@ -26032,7 +26044,7 @@
         <v>177</v>
       </c>
       <c r="B370" s="1">
-        <v>45869</v>
+        <v>45869.708333333336</v>
       </c>
       <c r="C370" s="0"/>
       <c r="D370" s="0"/>
@@ -26087,10 +26099,14 @@
         <v>178</v>
       </c>
       <c r="B371" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C371" s="0"/>
-      <c r="D371" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C371" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D371" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E371" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26144,10 +26160,14 @@
         <v>178</v>
       </c>
       <c r="B372" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C372" s="0"/>
-      <c r="D372" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C372" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D372" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E372" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26201,10 +26221,14 @@
         <v>178</v>
       </c>
       <c r="B373" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C373" s="0"/>
-      <c r="D373" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C373" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D373" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E373" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26258,10 +26282,14 @@
         <v>178</v>
       </c>
       <c r="B374" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C374" s="0"/>
-      <c r="D374" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C374" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D374" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E374" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26315,10 +26343,14 @@
         <v>178</v>
       </c>
       <c r="B375" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C375" s="0"/>
-      <c r="D375" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C375" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D375" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E375" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26372,10 +26404,14 @@
         <v>178</v>
       </c>
       <c r="B376" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C376" s="0"/>
-      <c r="D376" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C376" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D376" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E376" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26429,10 +26465,14 @@
         <v>178</v>
       </c>
       <c r="B377" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C377" s="0"/>
-      <c r="D377" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C377" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D377" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E377" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26486,10 +26526,14 @@
         <v>178</v>
       </c>
       <c r="B378" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C378" s="0"/>
-      <c r="D378" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C378" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D378" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E378" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26543,10 +26587,14 @@
         <v>178</v>
       </c>
       <c r="B379" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C379" s="0"/>
-      <c r="D379" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C379" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D379" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E379" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26600,10 +26648,14 @@
         <v>178</v>
       </c>
       <c r="B380" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C380" s="0"/>
-      <c r="D380" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C380" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D380" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E380" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26657,10 +26709,14 @@
         <v>178</v>
       </c>
       <c r="B381" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C381" s="0"/>
-      <c r="D381" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C381" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D381" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E381" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26714,10 +26770,14 @@
         <v>178</v>
       </c>
       <c r="B382" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C382" s="0"/>
-      <c r="D382" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C382" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D382" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E382" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26771,10 +26831,14 @@
         <v>178</v>
       </c>
       <c r="B383" s="1">
-        <v>45882</v>
-      </c>
-      <c r="C383" s="0"/>
-      <c r="D383" s="0"/>
+        <v>45882.541412037041</v>
+      </c>
+      <c r="C383" s="0">
+        <v>84.504000000000005</v>
+      </c>
+      <c r="D383" s="0">
+        <v>21.976600000000001</v>
+      </c>
       <c r="E383" s="0">
         <v>0.68999999999999995</v>
       </c>
@@ -26828,10 +26892,14 @@
         <v>179</v>
       </c>
       <c r="B384" s="1">
-        <v>45892</v>
-      </c>
-      <c r="C384" s="0"/>
-      <c r="D384" s="0"/>
+        <v>45892.6875</v>
+      </c>
+      <c r="C384" s="0">
+        <v>84.185699999999997</v>
+      </c>
+      <c r="D384" s="0">
+        <v>18.134799999999998</v>
+      </c>
       <c r="E384" s="0">
         <v>0.23000000000000001</v>
       </c>
@@ -26885,10 +26953,14 @@
         <v>179</v>
       </c>
       <c r="B385" s="1">
-        <v>45892</v>
-      </c>
-      <c r="C385" s="0"/>
-      <c r="D385" s="0"/>
+        <v>45892.6875</v>
+      </c>
+      <c r="C385" s="0">
+        <v>84.185699999999997</v>
+      </c>
+      <c r="D385" s="0">
+        <v>18.134799999999998</v>
+      </c>
       <c r="E385" s="0">
         <v>0.23000000000000001</v>
       </c>
@@ -26942,10 +27014,14 @@
         <v>179</v>
       </c>
       <c r="B386" s="1">
-        <v>45892</v>
-      </c>
-      <c r="C386" s="0"/>
-      <c r="D386" s="0"/>
+        <v>45892.6875</v>
+      </c>
+      <c r="C386" s="0">
+        <v>84.185699999999997</v>
+      </c>
+      <c r="D386" s="0">
+        <v>18.134799999999998</v>
+      </c>
       <c r="E386" s="0">
         <v>0.23000000000000001</v>
       </c>
@@ -26999,10 +27075,14 @@
         <v>179</v>
       </c>
       <c r="B387" s="1">
-        <v>45892</v>
-      </c>
-      <c r="C387" s="0"/>
-      <c r="D387" s="0"/>
+        <v>45892.6875</v>
+      </c>
+      <c r="C387" s="0">
+        <v>84.185699999999997</v>
+      </c>
+      <c r="D387" s="0">
+        <v>18.134799999999998</v>
+      </c>
       <c r="E387" s="0">
         <v>0.23000000000000001</v>
       </c>
@@ -27056,10 +27136,14 @@
         <v>179</v>
       </c>
       <c r="B388" s="1">
-        <v>45892</v>
-      </c>
-      <c r="C388" s="0"/>
-      <c r="D388" s="0"/>
+        <v>45892.6875</v>
+      </c>
+      <c r="C388" s="0">
+        <v>84.185699999999997</v>
+      </c>
+      <c r="D388" s="0">
+        <v>18.134799999999998</v>
+      </c>
       <c r="E388" s="0">
         <v>0.23000000000000001</v>
       </c>
@@ -27113,7 +27197,7 @@
         <v>181</v>
       </c>
       <c r="B389" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C389" s="0"/>
       <c r="D389" s="0"/>
@@ -27170,7 +27254,7 @@
         <v>181</v>
       </c>
       <c r="B390" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C390" s="0"/>
       <c r="D390" s="0"/>
@@ -27227,7 +27311,7 @@
         <v>181</v>
       </c>
       <c r="B391" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C391" s="0"/>
       <c r="D391" s="0"/>
@@ -27284,7 +27368,7 @@
         <v>181</v>
       </c>
       <c r="B392" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C392" s="0"/>
       <c r="D392" s="0"/>
@@ -27341,7 +27425,7 @@
         <v>181</v>
       </c>
       <c r="B393" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C393" s="0"/>
       <c r="D393" s="0"/>
@@ -27398,7 +27482,7 @@
         <v>181</v>
       </c>
       <c r="B394" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C394" s="0"/>
       <c r="D394" s="0"/>
@@ -27455,7 +27539,7 @@
         <v>181</v>
       </c>
       <c r="B395" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C395" s="0"/>
       <c r="D395" s="0"/>
@@ -27512,7 +27596,7 @@
         <v>181</v>
       </c>
       <c r="B396" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C396" s="0"/>
       <c r="D396" s="0"/>
@@ -27569,7 +27653,7 @@
         <v>181</v>
       </c>
       <c r="B397" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C397" s="0"/>
       <c r="D397" s="0"/>
@@ -27626,7 +27710,7 @@
         <v>181</v>
       </c>
       <c r="B398" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C398" s="0"/>
       <c r="D398" s="0"/>
@@ -27683,7 +27767,7 @@
         <v>181</v>
       </c>
       <c r="B399" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C399" s="0"/>
       <c r="D399" s="0"/>
@@ -27740,7 +27824,7 @@
         <v>181</v>
       </c>
       <c r="B400" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C400" s="0"/>
       <c r="D400" s="0"/>
@@ -27797,7 +27881,7 @@
         <v>181</v>
       </c>
       <c r="B401" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C401" s="0"/>
       <c r="D401" s="0"/>
@@ -27854,7 +27938,7 @@
         <v>181</v>
       </c>
       <c r="B402" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C402" s="0"/>
       <c r="D402" s="0"/>
@@ -27911,7 +27995,7 @@
         <v>181</v>
       </c>
       <c r="B403" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C403" s="0"/>
       <c r="D403" s="0"/>
@@ -27968,7 +28052,7 @@
         <v>181</v>
       </c>
       <c r="B404" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C404" s="0"/>
       <c r="D404" s="0"/>
@@ -28025,7 +28109,7 @@
         <v>181</v>
       </c>
       <c r="B405" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C405" s="0"/>
       <c r="D405" s="0"/>
@@ -28080,7 +28164,7 @@
         <v>181</v>
       </c>
       <c r="B406" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C406" s="0"/>
       <c r="D406" s="0"/>
@@ -28135,7 +28219,7 @@
         <v>181</v>
       </c>
       <c r="B407" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C407" s="0"/>
       <c r="D407" s="0"/>
@@ -28190,7 +28274,7 @@
         <v>181</v>
       </c>
       <c r="B408" s="1">
-        <v>45874</v>
+        <v>45874.666666666664</v>
       </c>
       <c r="C408" s="0"/>
       <c r="D408" s="0"/>
@@ -28245,10 +28329,14 @@
         <v>182</v>
       </c>
       <c r="B409" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C409" s="0"/>
-      <c r="D409" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C409" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D409" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E409" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28302,10 +28390,14 @@
         <v>182</v>
       </c>
       <c r="B410" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C410" s="0"/>
-      <c r="D410" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C410" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D410" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E410" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28359,10 +28451,14 @@
         <v>182</v>
       </c>
       <c r="B411" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C411" s="0"/>
-      <c r="D411" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C411" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D411" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E411" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28416,10 +28512,14 @@
         <v>182</v>
       </c>
       <c r="B412" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C412" s="0"/>
-      <c r="D412" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C412" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D412" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E412" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28473,10 +28573,14 @@
         <v>182</v>
       </c>
       <c r="B413" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C413" s="0"/>
-      <c r="D413" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C413" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D413" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E413" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28530,10 +28634,14 @@
         <v>182</v>
       </c>
       <c r="B414" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C414" s="0"/>
-      <c r="D414" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C414" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D414" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E414" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28587,10 +28695,14 @@
         <v>182</v>
       </c>
       <c r="B415" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C415" s="0"/>
-      <c r="D415" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C415" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D415" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E415" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28644,10 +28756,14 @@
         <v>182</v>
       </c>
       <c r="B416" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C416" s="0"/>
-      <c r="D416" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C416" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D416" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E416" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28701,10 +28817,14 @@
         <v>182</v>
       </c>
       <c r="B417" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C417" s="0"/>
-      <c r="D417" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C417" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D417" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E417" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28758,10 +28878,14 @@
         <v>182</v>
       </c>
       <c r="B418" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C418" s="0"/>
-      <c r="D418" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C418" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D418" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E418" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28815,10 +28939,14 @@
         <v>182</v>
       </c>
       <c r="B419" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C419" s="0"/>
-      <c r="D419" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C419" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D419" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E419" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28872,10 +29000,14 @@
         <v>182</v>
       </c>
       <c r="B420" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C420" s="0"/>
-      <c r="D420" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C420" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D420" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E420" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28929,10 +29061,14 @@
         <v>182</v>
       </c>
       <c r="B421" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C421" s="0"/>
-      <c r="D421" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C421" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D421" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E421" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -28986,10 +29122,14 @@
         <v>182</v>
       </c>
       <c r="B422" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C422" s="0"/>
-      <c r="D422" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C422" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D422" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E422" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29043,10 +29183,14 @@
         <v>182</v>
       </c>
       <c r="B423" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C423" s="0"/>
-      <c r="D423" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C423" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D423" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E423" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29100,10 +29244,14 @@
         <v>182</v>
       </c>
       <c r="B424" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C424" s="0"/>
-      <c r="D424" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C424" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D424" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E424" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29157,10 +29305,14 @@
         <v>182</v>
       </c>
       <c r="B425" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C425" s="0"/>
-      <c r="D425" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C425" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D425" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E425" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29214,10 +29366,14 @@
         <v>182</v>
       </c>
       <c r="B426" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C426" s="0"/>
-      <c r="D426" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C426" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D426" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E426" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29271,10 +29427,14 @@
         <v>182</v>
       </c>
       <c r="B427" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C427" s="0"/>
-      <c r="D427" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C427" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D427" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E427" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29328,10 +29488,14 @@
         <v>182</v>
       </c>
       <c r="B428" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C428" s="0"/>
-      <c r="D428" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C428" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D428" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E428" s="0">
         <v>1.3799999999999999</v>
       </c>
@@ -29385,10 +29549,14 @@
         <v>182</v>
       </c>
       <c r="B429" s="1">
-        <v>45886</v>
-      </c>
-      <c r="C429" s="0"/>
-      <c r="D429" s="0"/>
+        <v>45886.625</v>
+      </c>
+      <c r="C429" s="0">
+        <v>82.950800000000001</v>
+      </c>
+      <c r="D429" s="0">
+        <v>-12.814399999999999</v>
+      </c>
       <c r="E429" s="0">
         <v>1.3799999999999999</v>
       </c>

--- a/Export/Coring_data_export.xlsx
+++ b/Export/Coring_data_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95878" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="114406" uniqueCount="186">
   <si>
     <t>Event label</t>
   </si>
@@ -568,6 +568,12 @@
   <si>
     <t>PS149_47-1</t>
   </si>
+  <si>
+    <t>depth center</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
 </sst>
 </file>
 
@@ -708,7 +714,7 @@
         <v>29</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2">
@@ -771,10 +777,10 @@
       </c>
       <c r="T2" s="0"/>
       <c r="U2" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.072999999999999995</v>
       </c>
       <c r="V2" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="W2" s="0" t="s">
         <v>31</v>
@@ -840,10 +846,10 @@
       </c>
       <c r="T3" s="0"/>
       <c r="U3" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.088999999999999996</v>
       </c>
       <c r="V3" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="W3" s="0" t="s">
         <v>31</v>
@@ -909,10 +915,10 @@
       </c>
       <c r="T4" s="0"/>
       <c r="U4" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
       <c r="V4" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="W4" s="0" t="s">
         <v>31</v>
@@ -978,10 +984,10 @@
       </c>
       <c r="T5" s="0"/>
       <c r="U5" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="V5" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="W5" s="0" t="s">
         <v>31</v>
@@ -1047,10 +1053,10 @@
       </c>
       <c r="T6" s="0"/>
       <c r="U6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.065000000000000002</v>
       </c>
       <c r="V6" s="0">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="W6" s="0" t="s">
         <v>31</v>
@@ -1119,7 +1125,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="V7" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="W7" s="0"/>
     </row>
@@ -1183,7 +1189,7 @@
       </c>
       <c r="T8" s="0"/>
       <c r="U8" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V8" s="0">
         <v>0.070000000000000007</v>
@@ -1252,10 +1258,10 @@
         <v>0.37</v>
       </c>
       <c r="U9" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V9" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.045999999999999999</v>
       </c>
       <c r="W9" s="0"/>
     </row>
@@ -1321,10 +1327,10 @@
         <v>0.26000000000000001</v>
       </c>
       <c r="U10" s="0">
-        <v>0.01</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="V10" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W10" s="0"/>
     </row>
@@ -1390,10 +1396,10 @@
         <v>0.23000000000000001</v>
       </c>
       <c r="U11" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V11" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="W11" s="0"/>
     </row>
@@ -1459,10 +1465,10 @@
         <v>0.22</v>
       </c>
       <c r="U12" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V12" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W12" s="0"/>
     </row>
@@ -1528,10 +1534,10 @@
         <v>0.23000000000000001</v>
       </c>
       <c r="U13" s="0">
-        <v>0</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="V13" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W13" s="0"/>
     </row>
@@ -1597,10 +1603,10 @@
         <v>0.20999999999999999</v>
       </c>
       <c r="U14" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="V14" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W14" s="0"/>
     </row>
@@ -1666,7 +1672,7 @@
         <v>0.19</v>
       </c>
       <c r="U15" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="V15" s="0">
         <v>0.02</v>
@@ -1733,10 +1739,10 @@
       </c>
       <c r="T16" s="0"/>
       <c r="U16" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
       <c r="V16" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="W16" s="0" t="s">
         <v>32</v>
@@ -1804,10 +1810,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U17" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="V17" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="W17" s="0" t="s">
         <v>33</v>
@@ -1875,10 +1881,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U18" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="V18" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
       <c r="W18" s="0"/>
     </row>
@@ -1947,7 +1953,7 @@
         <v>0.01</v>
       </c>
       <c r="V19" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W19" s="0"/>
     </row>
@@ -2016,7 +2022,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="V20" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="W20" s="0" t="s">
         <v>31</v>
@@ -2084,10 +2090,10 @@
         <v>0.16</v>
       </c>
       <c r="U21" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V21" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W21" s="0"/>
     </row>
@@ -2153,10 +2159,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U22" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V22" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W22" s="0"/>
     </row>
@@ -2222,7 +2228,7 @@
         <v>0.13</v>
       </c>
       <c r="U23" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V23" s="0">
         <v>0.02</v>
@@ -2294,7 +2300,7 @@
         <v>0.01</v>
       </c>
       <c r="V24" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W24" s="0" t="s">
         <v>34</v>
@@ -2362,10 +2368,10 @@
         <v>0.12</v>
       </c>
       <c r="U25" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V25" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="W25" s="0" t="s">
         <v>34</v>
@@ -2433,7 +2439,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U26" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V26" s="0">
         <v>0.040000000000000001</v>
@@ -2504,10 +2510,10 @@
         <v>0.13</v>
       </c>
       <c r="U27" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V27" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W27" s="0" t="s">
         <v>36</v>
@@ -2575,10 +2581,10 @@
         <v>0.40000000000000002</v>
       </c>
       <c r="U28" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="V28" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="W28" s="0" t="s">
         <v>34</v>
@@ -2646,10 +2652,10 @@
         <v>0.12</v>
       </c>
       <c r="U29" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V29" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W29" s="0"/>
     </row>
@@ -2715,10 +2721,10 @@
         <v>0.12</v>
       </c>
       <c r="U30" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V30" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="W30" s="0" t="s">
         <v>37</v>
@@ -2789,7 +2795,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V31" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W31" s="0"/>
     </row>
@@ -2855,10 +2861,10 @@
         <v>0.12</v>
       </c>
       <c r="U32" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V32" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W32" s="0" t="s">
         <v>38</v>
@@ -2926,10 +2932,10 @@
         <v>0.13</v>
       </c>
       <c r="U33" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V33" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W33" s="0" t="s">
         <v>38</v>
@@ -2997,10 +3003,10 @@
         <v>0.11</v>
       </c>
       <c r="U34" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="V34" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.067000000000000004</v>
       </c>
       <c r="W34" s="0" t="s">
         <v>39</v>
@@ -3071,7 +3077,7 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="V35" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
       <c r="W35" s="0" t="s">
         <v>40</v>
@@ -3139,10 +3145,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U36" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="V36" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
       <c r="W36" s="0" t="s">
         <v>41</v>
@@ -3210,10 +3216,10 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="U37" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="V37" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="W37" s="0" t="s">
         <v>42</v>
@@ -3281,10 +3287,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U38" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.076999999999999999</v>
       </c>
       <c r="V38" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="W38" s="0" t="s">
         <v>43</v>
@@ -3352,7 +3358,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U39" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="V39" s="0">
         <v>0.059999999999999998</v>
@@ -3426,7 +3432,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="V40" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
       <c r="W40" s="0" t="s">
         <v>41</v>
@@ -3494,10 +3500,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U41" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
       <c r="V41" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="W41" s="0" t="s">
         <v>42</v>
@@ -3565,7 +3571,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U42" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="V42" s="0">
         <v>0.040000000000000001</v>
@@ -3634,10 +3640,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U43" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="V43" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="W43" s="0" t="s">
         <v>44</v>
@@ -3705,10 +3711,10 @@
         <v>0.12</v>
       </c>
       <c r="U44" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="V44" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="W44" s="0" t="s">
         <v>45</v>
@@ -3776,10 +3782,10 @@
         <v>0.11</v>
       </c>
       <c r="U45" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V45" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W45" s="0"/>
     </row>
@@ -3916,10 +3922,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U47" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V47" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W47" s="0" t="s">
         <v>47</v>
@@ -3987,10 +3993,10 @@
         <v>0.11</v>
       </c>
       <c r="U48" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V48" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W48" s="0"/>
     </row>
@@ -4056,10 +4062,10 @@
         <v>0.12</v>
       </c>
       <c r="U49" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V49" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W49" s="0"/>
     </row>
@@ -4125,10 +4131,10 @@
         <v>0.11</v>
       </c>
       <c r="U50" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V50" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W50" s="0"/>
     </row>
@@ -4194,7 +4200,7 @@
         <v>0.12</v>
       </c>
       <c r="U51" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V51" s="0">
         <v>0.02</v>
@@ -4337,7 +4343,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V53" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="W53" s="0" t="s">
         <v>48</v>
@@ -4405,10 +4411,10 @@
         <v>0.13</v>
       </c>
       <c r="U54" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V54" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="W54" s="0" t="s">
         <v>49</v>
@@ -4547,10 +4553,10 @@
         <v>0.13</v>
       </c>
       <c r="U56" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="V56" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="W56" s="0" t="s">
         <v>39</v>
@@ -4618,10 +4624,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U57" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="V57" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="W57" s="0"/>
     </row>
@@ -4687,10 +4693,10 @@
         <v>0.12</v>
       </c>
       <c r="U58" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V58" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="W58" s="0"/>
     </row>
@@ -4756,10 +4762,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U59" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V59" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W59" s="0"/>
     </row>
@@ -4825,10 +4831,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U60" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="V60" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="W60" s="0" t="s">
         <v>51</v>
@@ -4896,10 +4902,10 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U61" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="V61" s="0">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="W61" s="0" t="s">
         <v>52</v>
@@ -4967,10 +4973,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U62" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="V62" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="W62" s="0" t="s">
         <v>52</v>
@@ -5038,10 +5044,10 @@
         <v>0.13</v>
       </c>
       <c r="U63" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
       <c r="V63" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
       <c r="W63" s="0" t="s">
         <v>53</v>
@@ -5109,10 +5115,10 @@
         <v>0.11</v>
       </c>
       <c r="U64" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.074999999999999997</v>
       </c>
       <c r="V64" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="W64" s="0" t="s">
         <v>53</v>
@@ -5180,10 +5186,10 @@
         <v>0.11</v>
       </c>
       <c r="U65" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="V65" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="W65" s="0"/>
     </row>
@@ -5249,10 +5255,10 @@
         <v>0.13</v>
       </c>
       <c r="U66" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.063</v>
       </c>
       <c r="V66" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
       <c r="W66" s="0" t="s">
         <v>54</v>
@@ -5320,7 +5326,7 @@
         <v>0.13</v>
       </c>
       <c r="U67" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V67" s="0">
         <v>0.050000000000000003</v>
@@ -5948,7 +5954,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="V78" s="0">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="W78" s="0" t="s">
         <v>57</v>
@@ -6016,10 +6022,10 @@
         <v>0.34000000000000002</v>
       </c>
       <c r="U79" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="V79" s="0">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="W79" s="0" t="s">
         <v>58</v>
@@ -6087,10 +6093,10 @@
         <v>0.23999999999999999</v>
       </c>
       <c r="U80" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="V80" s="0">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="W80" s="0" t="s">
         <v>59</v>
@@ -6158,10 +6164,10 @@
         <v>0.13</v>
       </c>
       <c r="U81" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
       <c r="V81" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="W81" s="0" t="s">
         <v>59</v>
@@ -6229,10 +6235,10 @@
         <v>0.16</v>
       </c>
       <c r="U82" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="V82" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
       <c r="W82" s="0" t="s">
         <v>60</v>
@@ -6300,10 +6306,10 @@
         <v>0.16</v>
       </c>
       <c r="U83" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="V83" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="W83" s="0" t="s">
         <v>61</v>
@@ -6371,10 +6377,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U84" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
       <c r="V84" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="W84" s="0" t="s">
         <v>62</v>
@@ -6442,7 +6448,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U85" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="V85" s="0">
         <v>0.050000000000000003</v>
@@ -6513,10 +6519,10 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U86" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="V86" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
       <c r="W86" s="0" t="s">
         <v>64</v>
@@ -6584,10 +6590,10 @@
         <v>0.16</v>
       </c>
       <c r="U87" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="V87" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="W87" s="0" t="s">
         <v>65</v>
@@ -6658,7 +6664,7 @@
         <v>0.02</v>
       </c>
       <c r="V88" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="W88" s="0" t="s">
         <v>66</v>
@@ -6726,7 +6732,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U89" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.048000000000000001</v>
       </c>
       <c r="V89" s="0">
         <v>0.059999999999999998</v>
@@ -6797,10 +6803,10 @@
         <v>0.11</v>
       </c>
       <c r="U90" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="V90" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W90" s="0" t="s">
         <v>66</v>
@@ -6868,10 +6874,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U91" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V91" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W91" s="0"/>
     </row>
@@ -6937,10 +6943,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U92" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
       <c r="V92" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="W92" s="0" t="s">
         <v>31</v>
@@ -7008,10 +7014,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U93" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="V93" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="W93" s="0" t="s">
         <v>67</v>
@@ -7079,10 +7085,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U94" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.065000000000000002</v>
       </c>
       <c r="V94" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="W94" s="0" t="s">
         <v>31</v>
@@ -7150,10 +7156,10 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U95" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V95" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W95" s="0"/>
     </row>
@@ -7219,10 +7225,10 @@
         <v>0.16</v>
       </c>
       <c r="U96" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V96" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="W96" s="0" t="s">
         <v>68</v>
@@ -7290,10 +7296,10 @@
         <v>0.16</v>
       </c>
       <c r="U97" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="V97" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.047</v>
       </c>
       <c r="W97" s="0" t="s">
         <v>31</v>
@@ -7361,7 +7367,7 @@
         <v>0.16</v>
       </c>
       <c r="U98" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.066000000000000003</v>
       </c>
       <c r="V98" s="0">
         <v>0.080000000000000002</v>
@@ -7430,7 +7436,7 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U99" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="V99" s="0">
         <v>0.050000000000000003</v>
@@ -7501,10 +7507,10 @@
         <v>0.16</v>
       </c>
       <c r="U100" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V100" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="W100" s="0" t="s">
         <v>31</v>
@@ -7572,10 +7578,10 @@
         <v>0.16</v>
       </c>
       <c r="U101" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="V101" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="W101" s="0"/>
     </row>
@@ -7641,10 +7647,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U102" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V102" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="W102" s="0" t="s">
         <v>69</v>
@@ -7712,10 +7718,10 @@
         <v>0.16</v>
       </c>
       <c r="U103" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V103" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="W103" s="0"/>
     </row>
@@ -7781,10 +7787,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U104" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V104" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W104" s="0"/>
     </row>
@@ -7850,7 +7856,7 @@
         <v>0.13</v>
       </c>
       <c r="U105" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V105" s="0">
         <v>0.029999999999999999</v>
@@ -7922,7 +7928,7 @@
         <v>0.02</v>
       </c>
       <c r="V106" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="W106" s="0"/>
     </row>
@@ -7991,7 +7997,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V107" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="W107" s="0" t="s">
         <v>70</v>
@@ -8059,10 +8065,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U108" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V108" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W108" s="0" t="s">
         <v>70</v>
@@ -8130,10 +8136,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U109" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V109" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W109" s="0" t="s">
         <v>70</v>
@@ -8204,7 +8210,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V110" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="W110" s="0" t="s">
         <v>71</v>
@@ -8272,10 +8278,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U111" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="V111" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="W111" s="0" t="s">
         <v>31</v>
@@ -8343,10 +8349,10 @@
         <v>0.12</v>
       </c>
       <c r="U112" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V112" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W112" s="0" t="s">
         <v>72</v>
@@ -8414,10 +8420,10 @@
         <v>0.12</v>
       </c>
       <c r="U113" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V113" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W113" s="0"/>
     </row>
@@ -8483,10 +8489,10 @@
         <v>0.13</v>
       </c>
       <c r="U114" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V114" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W114" s="0"/>
     </row>
@@ -8552,10 +8558,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U115" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V115" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W115" s="0"/>
     </row>
@@ -8621,10 +8627,10 @@
         <v>0.13</v>
       </c>
       <c r="U116" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V116" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W116" s="0"/>
     </row>
@@ -8693,7 +8699,7 @@
         <v>0.01</v>
       </c>
       <c r="V117" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W117" s="0"/>
     </row>
@@ -8759,10 +8765,10 @@
         <v>0.12</v>
       </c>
       <c r="U118" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V118" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W118" s="0"/>
     </row>
@@ -8828,10 +8834,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U119" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V119" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W119" s="0"/>
     </row>
@@ -8897,10 +8903,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U120" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V120" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W120" s="0"/>
     </row>
@@ -8966,10 +8972,10 @@
         <v>0.19</v>
       </c>
       <c r="U121" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.066000000000000003</v>
       </c>
       <c r="V121" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
       <c r="W121" s="0" t="s">
         <v>73</v>
@@ -9037,10 +9043,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U122" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="V122" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="W122" s="0" t="s">
         <v>59</v>
@@ -9108,10 +9114,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U123" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.090999999999999998</v>
       </c>
       <c r="V123" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.099000000000000005</v>
       </c>
       <c r="W123" s="0" t="s">
         <v>74</v>
@@ -9179,10 +9185,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U124" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="V124" s="0">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
       <c r="W124" s="0" t="s">
         <v>59</v>
@@ -9250,10 +9256,10 @@
         <v>0.22</v>
       </c>
       <c r="U125" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.075999999999999998</v>
       </c>
       <c r="V125" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
       <c r="W125" s="0" t="s">
         <v>75</v>
@@ -9321,10 +9327,10 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="U126" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="V126" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="W126" s="0" t="s">
         <v>74</v>
@@ -9392,10 +9398,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="U127" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V127" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.047</v>
       </c>
       <c r="W127" s="0" t="s">
         <v>76</v>
@@ -9463,7 +9469,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="U128" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="V128" s="0">
         <v>0.059999999999999998</v>
@@ -9537,7 +9543,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V129" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="W129" s="0" t="s">
         <v>77</v>
@@ -9605,10 +9611,10 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U130" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V130" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W130" s="0"/>
     </row>
@@ -9674,10 +9680,10 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U131" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V131" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W131" s="0"/>
     </row>
@@ -9743,10 +9749,10 @@
         <v>0.19</v>
       </c>
       <c r="U132" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="V132" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.043999999999999997</v>
       </c>
       <c r="W132" s="0"/>
     </row>
@@ -9815,7 +9821,7 @@
         <v>0.02</v>
       </c>
       <c r="V133" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="W133" s="0"/>
     </row>
@@ -9881,10 +9887,10 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U134" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V134" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="W134" s="0" t="s">
         <v>78</v>
@@ -9952,10 +9958,10 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U135" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V135" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="W135" s="0" t="s">
         <v>78</v>
@@ -10023,10 +10029,10 @@
         <v>0.16</v>
       </c>
       <c r="U136" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="V136" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="W136" s="0"/>
     </row>
@@ -10092,10 +10098,10 @@
         <v>0.12</v>
       </c>
       <c r="U137" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="V137" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W137" s="0" t="s">
         <v>79</v>
@@ -10163,10 +10169,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U138" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V138" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W138" s="0"/>
     </row>
@@ -10370,10 +10376,10 @@
         <v>0.12</v>
       </c>
       <c r="U141" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="V141" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="W141" s="0" t="s">
         <v>80</v>
@@ -10441,10 +10447,10 @@
         <v>0.12</v>
       </c>
       <c r="U142" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V142" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="W142" s="0"/>
     </row>
@@ -10510,10 +10516,10 @@
         <v>0.11</v>
       </c>
       <c r="U143" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V143" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W143" s="0"/>
     </row>
@@ -10579,10 +10585,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U144" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V144" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W144" s="0"/>
     </row>
@@ -10651,7 +10657,7 @@
         <v>0.01</v>
       </c>
       <c r="V145" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W145" s="0"/>
     </row>
@@ -10713,10 +10719,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U146" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="V146" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="W146" s="0" t="s">
         <v>81</v>
@@ -10780,10 +10786,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U147" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="V147" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="W147" s="0" t="s">
         <v>82</v>
@@ -10850,7 +10856,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="V148" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="W148" s="0" t="s">
         <v>83</v>
@@ -10914,10 +10920,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U149" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="V149" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="W149" s="0" t="s">
         <v>84</v>
@@ -10981,10 +10987,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U150" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="V150" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="W150" s="0" t="s">
         <v>61</v>
@@ -11048,10 +11054,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U151" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V151" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.043999999999999997</v>
       </c>
       <c r="W151" s="0" t="s">
         <v>85</v>
@@ -11118,7 +11124,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="V152" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="W152" s="0" t="s">
         <v>86</v>
@@ -11185,7 +11191,7 @@
         <v>0.02</v>
       </c>
       <c r="V153" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W153" s="0" t="s">
         <v>87</v>
@@ -11249,10 +11255,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U154" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V154" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="W154" s="0" t="s">
         <v>88</v>
@@ -11316,7 +11322,7 @@
         <v>0.12</v>
       </c>
       <c r="U155" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V155" s="0">
         <v>0.02</v>
@@ -11381,7 +11387,7 @@
         <v>0.13</v>
       </c>
       <c r="U156" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V156" s="0">
         <v>0.02</v>
@@ -11446,10 +11452,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U157" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V157" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="W157" s="0"/>
     </row>
@@ -11511,7 +11517,7 @@
         <v>0.13</v>
       </c>
       <c r="U158" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V158" s="0">
         <v>0.02</v>
@@ -11576,10 +11582,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U159" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V159" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W159" s="0" t="s">
         <v>89</v>
@@ -11643,10 +11649,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U160" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V160" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W160" s="0" t="s">
         <v>89</v>
@@ -11710,10 +11716,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U161" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V161" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W161" s="0"/>
     </row>
@@ -11840,10 +11846,10 @@
         <v>0.11</v>
       </c>
       <c r="U163" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V163" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W163" s="0" t="s">
         <v>68</v>
@@ -11907,10 +11913,10 @@
         <v>0.12</v>
       </c>
       <c r="U164" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V164" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W164" s="0"/>
     </row>
@@ -11972,10 +11978,10 @@
         <v>0.12</v>
       </c>
       <c r="U165" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V165" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W165" s="0"/>
     </row>
@@ -12037,10 +12043,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U166" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V166" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W166" s="0"/>
     </row>
@@ -12105,7 +12111,7 @@
         <v>0.01</v>
       </c>
       <c r="V167" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W167" s="0"/>
     </row>
@@ -12167,10 +12173,10 @@
         <v>0.13</v>
       </c>
       <c r="U168" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V168" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W168" s="0"/>
     </row>
@@ -12232,10 +12238,10 @@
         <v>0.13</v>
       </c>
       <c r="U169" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V169" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W169" s="0"/>
     </row>
@@ -12297,10 +12303,10 @@
         <v>0.13</v>
       </c>
       <c r="U170" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V170" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W170" s="0"/>
     </row>
@@ -12362,10 +12368,10 @@
         <v>0.13</v>
       </c>
       <c r="U171" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V171" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W171" s="0"/>
     </row>
@@ -12427,10 +12433,10 @@
         <v>0.12</v>
       </c>
       <c r="U172" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V172" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W172" s="0" t="s">
         <v>90</v>
@@ -12494,10 +12500,10 @@
         <v>0.11</v>
       </c>
       <c r="U173" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="V173" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W173" s="0" t="s">
         <v>91</v>
@@ -12561,10 +12567,10 @@
         <v>0.12</v>
       </c>
       <c r="U174" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V174" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W174" s="0" t="s">
         <v>90</v>
@@ -12628,10 +12634,10 @@
         <v>0.12</v>
       </c>
       <c r="U175" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V175" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W175" s="0" t="s">
         <v>90</v>
@@ -12695,10 +12701,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U176" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V176" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="W176" s="0" t="s">
         <v>90</v>
@@ -12762,7 +12768,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U177" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="V177" s="0">
         <v>0.040000000000000001</v>
@@ -12829,7 +12835,7 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U178" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="V178" s="0">
         <v>0.029999999999999999</v>
@@ -12896,10 +12902,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U179" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V179" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W179" s="0" t="s">
         <v>90</v>
@@ -12963,10 +12969,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U180" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V180" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W180" s="0" t="s">
         <v>90</v>
@@ -13030,10 +13036,10 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="U181" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V181" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="W181" s="0"/>
     </row>
@@ -13100,7 +13106,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="V182" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="W182" s="0" t="s">
         <v>57</v>
@@ -13168,10 +13174,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U183" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
       <c r="V183" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="W183" s="0" t="s">
         <v>57</v>
@@ -13239,10 +13245,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U184" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.065000000000000002</v>
       </c>
       <c r="V184" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
       <c r="W184" s="0" t="s">
         <v>92</v>
@@ -13313,7 +13319,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="V185" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="W185" s="0" t="s">
         <v>57</v>
@@ -13381,10 +13387,10 @@
         <v>0.20999999999999999</v>
       </c>
       <c r="U186" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
       <c r="V186" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="W186" s="0" t="s">
         <v>93</v>
@@ -13452,7 +13458,7 @@
         <v>0.12</v>
       </c>
       <c r="U187" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.088999999999999996</v>
       </c>
       <c r="V187" s="0">
         <v>0.10000000000000001</v>
@@ -13523,10 +13529,10 @@
         <v>0.13</v>
       </c>
       <c r="U188" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
       <c r="V188" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.072999999999999995</v>
       </c>
       <c r="W188" s="0" t="s">
         <v>94</v>
@@ -13594,10 +13600,10 @@
         <v>0.19</v>
       </c>
       <c r="U189" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
       <c r="V189" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.090999999999999998</v>
       </c>
       <c r="W189" s="0" t="s">
         <v>95</v>
@@ -13665,7 +13671,7 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U190" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="V190" s="0">
         <v>0.10000000000000001</v>
@@ -13739,7 +13745,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="V191" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="W191" s="0" t="s">
         <v>96</v>
@@ -13807,10 +13813,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U192" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="V192" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="W192" s="0" t="s">
         <v>96</v>
@@ -13878,10 +13884,10 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U193" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V193" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="W193" s="0" t="s">
         <v>97</v>
@@ -13949,7 +13955,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U194" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.075999999999999998</v>
       </c>
       <c r="V194" s="0">
         <v>0.089999999999999997</v>
@@ -14020,10 +14026,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U195" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="V195" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="W195" s="0" t="s">
         <v>99</v>
@@ -14091,10 +14097,10 @@
         <v>0.16</v>
       </c>
       <c r="U196" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="V196" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.066000000000000003</v>
       </c>
       <c r="W196" s="0" t="s">
         <v>99</v>
@@ -14162,10 +14168,10 @@
         <v>0.19</v>
       </c>
       <c r="U197" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="V197" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="W197" s="0" t="s">
         <v>100</v>
@@ -14233,10 +14239,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U198" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="V198" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="W198" s="0" t="s">
         <v>94</v>
@@ -14304,10 +14310,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U199" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V199" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.033000000000000002</v>
       </c>
       <c r="W199" s="0" t="s">
         <v>94</v>
@@ -14375,10 +14381,10 @@
         <v>0.13</v>
       </c>
       <c r="U200" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V200" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W200" s="0" t="s">
         <v>94</v>
@@ -14446,10 +14452,10 @@
         <v>0.11</v>
       </c>
       <c r="U201" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V201" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="W201" s="0"/>
     </row>
@@ -14515,10 +14521,10 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="U202" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.047</v>
       </c>
       <c r="V202" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.063</v>
       </c>
       <c r="W202" s="0" t="s">
         <v>101</v>
@@ -14586,10 +14592,10 @@
         <v>0.11</v>
       </c>
       <c r="U203" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="V203" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="W203" s="0" t="s">
         <v>102</v>
@@ -14660,7 +14666,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="V204" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="W204" s="0" t="s">
         <v>103</v>
@@ -14728,7 +14734,7 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="U205" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="V205" s="0">
         <v>0.070000000000000007</v>
@@ -14799,10 +14805,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U206" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="V206" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.067000000000000004</v>
       </c>
       <c r="W206" s="0" t="s">
         <v>104</v>
@@ -14870,10 +14876,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U207" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="V207" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="W207" s="0" t="s">
         <v>105</v>
@@ -14941,10 +14947,10 @@
         <v>0.12</v>
       </c>
       <c r="U208" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
       <c r="V208" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="W208" s="0" t="s">
         <v>106</v>
@@ -15012,10 +15018,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U209" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
       <c r="V209" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
       <c r="W209" s="0" t="s">
         <v>107</v>
@@ -15083,10 +15089,10 @@
         <v>0.12</v>
       </c>
       <c r="U210" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V210" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W210" s="0" t="s">
         <v>107</v>
@@ -15154,10 +15160,10 @@
         <v>0.11</v>
       </c>
       <c r="U211" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="V211" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="W211" s="0" t="s">
         <v>108</v>
@@ -15225,10 +15231,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U212" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="V212" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="W212" s="0" t="s">
         <v>108</v>
@@ -15296,10 +15302,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U213" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V213" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="W213" s="0" t="s">
         <v>108</v>
@@ -15370,7 +15376,7 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="V214" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="W214" s="0" t="s">
         <v>108</v>
@@ -15438,10 +15444,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U215" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="V215" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="W215" s="0" t="s">
         <v>109</v>
@@ -15509,10 +15515,10 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="U216" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="V216" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.055</v>
       </c>
       <c r="W216" s="0" t="s">
         <v>61</v>
@@ -15583,7 +15589,7 @@
         <v>0.02</v>
       </c>
       <c r="V217" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W217" s="0" t="s">
         <v>61</v>
@@ -15651,10 +15657,10 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="U218" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V218" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="W218" s="0" t="s">
         <v>61</v>
@@ -15722,10 +15728,10 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="U219" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V219" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W219" s="0" t="s">
         <v>61</v>
@@ -15793,10 +15799,10 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U220" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V220" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W220" s="0" t="s">
         <v>110</v>
@@ -15864,10 +15870,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U221" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="V221" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W221" s="0" t="s">
         <v>110</v>
@@ -15935,7 +15941,7 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U222" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V222" s="0">
         <v>0.02</v>
@@ -16006,10 +16012,10 @@
         <v>0.13</v>
       </c>
       <c r="U223" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V223" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="W223" s="0" t="s">
         <v>111</v>
@@ -16077,7 +16083,7 @@
         <v>0.11</v>
       </c>
       <c r="U224" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V224" s="0">
         <v>0.029999999999999999</v>
@@ -16148,10 +16154,10 @@
         <v>0.11</v>
       </c>
       <c r="U225" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V225" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.033000000000000002</v>
       </c>
       <c r="W225" s="0" t="s">
         <v>113</v>
@@ -16219,10 +16225,10 @@
         <v>0.12</v>
       </c>
       <c r="U226" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="V226" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W226" s="0" t="s">
         <v>114</v>
@@ -16290,10 +16296,10 @@
         <v>0.12</v>
       </c>
       <c r="U227" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V227" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W227" s="0" t="s">
         <v>114</v>
@@ -16361,10 +16367,10 @@
         <v>0.12</v>
       </c>
       <c r="U228" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V228" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W228" s="0" t="s">
         <v>115</v>
@@ -16432,10 +16438,10 @@
         <v>0.11</v>
       </c>
       <c r="U229" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V229" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W229" s="0" t="s">
         <v>116</v>
@@ -16503,10 +16509,10 @@
         <v>0.11</v>
       </c>
       <c r="U230" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V230" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W230" s="0"/>
     </row>
@@ -16572,10 +16578,10 @@
         <v>0.11</v>
       </c>
       <c r="U231" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V231" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W231" s="0" t="s">
         <v>117</v>
@@ -16646,7 +16652,7 @@
         <v>0.01</v>
       </c>
       <c r="V232" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W232" s="0"/>
     </row>
@@ -16712,10 +16718,10 @@
         <v>0.11</v>
       </c>
       <c r="U233" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V233" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W233" s="0"/>
     </row>
@@ -16850,10 +16856,10 @@
         <v>0.12</v>
       </c>
       <c r="U235" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V235" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W235" s="0"/>
     </row>
@@ -16919,10 +16925,10 @@
         <v>0.12</v>
       </c>
       <c r="U236" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V236" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W236" s="0" t="s">
         <v>118</v>
@@ -16990,7 +16996,7 @@
         <v>0.12</v>
       </c>
       <c r="U237" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V237" s="0">
         <v>0.029999999999999999</v>
@@ -17059,10 +17065,10 @@
         <v>0.12</v>
       </c>
       <c r="U238" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V238" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W238" s="0" t="s">
         <v>119</v>
@@ -17130,10 +17136,10 @@
         <v>0.11</v>
       </c>
       <c r="U239" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V239" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W239" s="0"/>
     </row>
@@ -17202,7 +17208,7 @@
         <v>0.01</v>
       </c>
       <c r="V240" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W240" s="0"/>
     </row>
@@ -17268,10 +17274,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U241" s="0">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V241" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="W241" s="0"/>
     </row>
@@ -17337,10 +17343,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U242" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V242" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W242" s="0"/>
     </row>
@@ -17406,10 +17412,10 @@
         <v>0.12</v>
       </c>
       <c r="U243" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V243" s="0">
-        <v>0.02</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W243" s="0"/>
     </row>
@@ -17475,10 +17481,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U244" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V244" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W244" s="0"/>
     </row>
@@ -17544,7 +17550,7 @@
         <v>0.13</v>
       </c>
       <c r="U245" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V245" s="0">
         <v>0.02</v>
@@ -17751,10 +17757,10 @@
         <v>0.11</v>
       </c>
       <c r="U248" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V248" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W248" s="0"/>
     </row>
@@ -17820,10 +17826,10 @@
         <v>0.16</v>
       </c>
       <c r="U249" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V249" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W249" s="0"/>
     </row>
@@ -17889,10 +17895,10 @@
         <v>0.19</v>
       </c>
       <c r="U250" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V250" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W250" s="0"/>
     </row>
@@ -17958,7 +17964,7 @@
         <v>0.13</v>
       </c>
       <c r="U251" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="V251" s="0">
         <v>0.070000000000000007</v>
@@ -18032,7 +18038,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="V252" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.043999999999999997</v>
       </c>
       <c r="W252" s="0" t="s">
         <v>89</v>
@@ -18100,10 +18106,10 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U253" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V253" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W253" s="0" t="s">
         <v>89</v>
@@ -18171,10 +18177,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U254" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.048000000000000001</v>
       </c>
       <c r="V254" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.055</v>
       </c>
       <c r="W254" s="0" t="s">
         <v>89</v>
@@ -18242,10 +18248,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U255" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="V255" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="W255" s="0" t="s">
         <v>89</v>
@@ -18313,10 +18319,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U256" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
       <c r="V256" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
       </c>
       <c r="W256" s="0" t="s">
         <v>120</v>
@@ -18384,10 +18390,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U257" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.047</v>
       </c>
       <c r="V257" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.056000000000000001</v>
       </c>
       <c r="W257" s="0" t="s">
         <v>89</v>
@@ -18455,10 +18461,10 @@
         <v>0.11</v>
       </c>
       <c r="U258" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="V258" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="W258" s="0" t="s">
         <v>89</v>
@@ -18597,10 +18603,10 @@
         <v>0.16</v>
       </c>
       <c r="U260" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="V260" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="W260" s="0" t="s">
         <v>62</v>
@@ -18668,7 +18674,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U261" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="V261" s="0">
         <v>0.029999999999999999</v>
@@ -18739,10 +18745,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U262" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V262" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W262" s="0" t="s">
         <v>122</v>
@@ -18810,10 +18816,10 @@
         <v>0.13</v>
       </c>
       <c r="U263" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V263" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="W263" s="0" t="s">
         <v>122</v>
@@ -18881,10 +18887,10 @@
         <v>0.12</v>
       </c>
       <c r="U264" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="V264" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W264" s="0" t="s">
         <v>122</v>
@@ -18952,10 +18958,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U265" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V265" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W265" s="0"/>
     </row>
@@ -19021,10 +19027,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U266" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V266" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W266" s="0" t="s">
         <v>90</v>
@@ -19092,10 +19098,10 @@
         <v>0.11</v>
       </c>
       <c r="U267" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V267" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W267" s="0"/>
     </row>
@@ -19161,10 +19167,10 @@
         <v>0.12</v>
       </c>
       <c r="U268" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="V268" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W268" s="0" t="s">
         <v>39</v>
@@ -19303,10 +19309,10 @@
         <v>0.12</v>
       </c>
       <c r="U270" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="V270" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="W270" s="0"/>
     </row>
@@ -19372,10 +19378,10 @@
         <v>0.12</v>
       </c>
       <c r="U271" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V271" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W271" s="0" t="s">
         <v>39</v>
@@ -19443,10 +19449,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U272" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="V272" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W272" s="0" t="s">
         <v>61</v>
@@ -19514,10 +19520,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U273" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V273" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W273" s="0"/>
     </row>
@@ -19583,10 +19589,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U274" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V274" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W274" s="0"/>
     </row>
@@ -19652,10 +19658,10 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="U275" s="0">
-        <v>0.01</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="V275" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W275" s="0"/>
     </row>
@@ -19721,10 +19727,10 @@
         <v>0.11</v>
       </c>
       <c r="U276" s="0">
-        <v>0.01</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="V276" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="W276" s="0"/>
     </row>
@@ -19790,10 +19796,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U277" s="0">
-        <v>0.01</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="V277" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="W277" s="0"/>
     </row>
@@ -19859,10 +19865,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U278" s="0">
-        <v>0</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="V278" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="W278" s="0"/>
     </row>
@@ -19928,10 +19934,10 @@
         <v>0.12</v>
       </c>
       <c r="U279" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V279" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W279" s="0"/>
     </row>
@@ -19997,10 +20003,10 @@
         <v>0.12</v>
       </c>
       <c r="U280" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V280" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W280" s="0"/>
     </row>
@@ -20066,10 +20072,10 @@
         <v>0.11</v>
       </c>
       <c r="U281" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V281" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W281" s="0"/>
     </row>
@@ -20135,10 +20141,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U282" s="0">
-        <v>0.01</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="V282" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="W282" s="0"/>
     </row>
@@ -20204,10 +20210,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U283" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V283" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="W283" s="0"/>
     </row>
@@ -20273,10 +20279,10 @@
         <v>0.11</v>
       </c>
       <c r="U284" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V284" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W284" s="0"/>
     </row>
@@ -20345,7 +20351,7 @@
         <v>0.01</v>
       </c>
       <c r="V285" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W285" s="0"/>
     </row>
@@ -20411,10 +20417,10 @@
         <v>0.19</v>
       </c>
       <c r="U286" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
       <c r="V286" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.099000000000000005</v>
       </c>
       <c r="W286" s="0" t="s">
         <v>123</v>
@@ -20482,10 +20488,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U287" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="V287" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="W287" s="0" t="s">
         <v>92</v>
@@ -20553,10 +20559,10 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="U288" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="V288" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
       <c r="W288" s="0" t="s">
         <v>124</v>
@@ -20624,10 +20630,10 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U289" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="V289" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="W289" s="0" t="s">
         <v>125</v>
@@ -20695,10 +20701,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U290" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.073999999999999996</v>
       </c>
       <c r="V290" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="W290" s="0" t="s">
         <v>57</v>
@@ -20766,10 +20772,10 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="U291" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.071999999999999995</v>
       </c>
       <c r="V291" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="W291" s="0" t="s">
         <v>126</v>
@@ -20837,10 +20843,10 @@
         <v>0.029999999999999999</v>
       </c>
       <c r="U292" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.056000000000000001</v>
       </c>
       <c r="V292" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="W292" s="0" t="s">
         <v>127</v>
@@ -20908,7 +20914,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U293" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="V293" s="0">
         <v>0.059999999999999998</v>
@@ -20982,7 +20988,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="V294" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.047</v>
       </c>
       <c r="W294" s="0" t="s">
         <v>126</v>
@@ -21050,7 +21056,7 @@
         <v>0.13</v>
       </c>
       <c r="U295" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V295" s="0">
         <v>0.050000000000000003</v>
@@ -21119,10 +21125,10 @@
         <v>0.11</v>
       </c>
       <c r="U296" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="V296" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="W296" s="0" t="s">
         <v>128</v>
@@ -21190,10 +21196,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U297" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.055</v>
       </c>
       <c r="V297" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
       <c r="W297" s="0" t="s">
         <v>127</v>
@@ -21261,10 +21267,10 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U298" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="V298" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.067000000000000004</v>
       </c>
       <c r="W298" s="0" t="s">
         <v>57</v>
@@ -21332,10 +21338,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U299" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V299" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="W299" s="0" t="s">
         <v>57</v>
@@ -21403,10 +21409,10 @@
         <v>0.11</v>
       </c>
       <c r="U300" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="V300" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.055</v>
       </c>
       <c r="W300" s="0" t="s">
         <v>66</v>
@@ -21474,10 +21480,10 @@
         <v>0.11</v>
       </c>
       <c r="U301" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="V301" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="W301" s="0" t="s">
         <v>66</v>
@@ -21545,10 +21551,10 @@
         <v>0.12</v>
       </c>
       <c r="U302" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V302" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="W302" s="0" t="s">
         <v>129</v>
@@ -21616,10 +21622,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U303" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V303" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W303" s="0" t="s">
         <v>130</v>
@@ -21687,10 +21693,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U304" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="V304" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="W304" s="0" t="s">
         <v>90</v>
@@ -21758,7 +21764,7 @@
         <v>0.13</v>
       </c>
       <c r="U305" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V305" s="0">
         <v>0.02</v>
@@ -21829,10 +21835,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U306" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V306" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="W306" s="0" t="s">
         <v>131</v>
@@ -21900,10 +21906,10 @@
         <v>0.11</v>
       </c>
       <c r="U307" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V307" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W307" s="0" t="s">
         <v>90</v>
@@ -21971,10 +21977,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U308" s="0">
-        <v>0</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="V308" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="W308" s="0" t="s">
         <v>90</v>
@@ -22042,10 +22048,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U309" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="V309" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="W309" s="0" t="s">
         <v>90</v>
@@ -22113,10 +22119,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U310" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="V310" s="0">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="W310" s="0" t="s">
         <v>90</v>
@@ -22184,10 +22190,10 @@
         <v>0.13</v>
       </c>
       <c r="U311" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V311" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W311" s="0" t="s">
         <v>90</v>
@@ -22255,10 +22261,10 @@
         <v>0.13</v>
       </c>
       <c r="U312" s="0">
-        <v>0</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="V312" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="W312" s="0" t="s">
         <v>90</v>
@@ -22326,10 +22332,10 @@
         <v>0.11</v>
       </c>
       <c r="U313" s="0">
-        <v>0.01</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="V313" s="0">
-        <v>0.01</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="W313" s="0" t="s">
         <v>90</v>
@@ -22397,10 +22403,10 @@
         <v>0.12</v>
       </c>
       <c r="U314" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V314" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W314" s="0" t="s">
         <v>90</v>
@@ -22468,10 +22474,10 @@
         <v>0.12</v>
       </c>
       <c r="U315" s="0">
-        <v>0</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="V315" s="0">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="W315" s="0" t="s">
         <v>90</v>
@@ -22539,10 +22545,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U316" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="V316" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="W316" s="0" t="s">
         <v>90</v>
@@ -22610,10 +22616,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U317" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="V317" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="W317" s="0" t="s">
         <v>132</v>
@@ -22681,10 +22687,10 @@
         <v>0.11</v>
       </c>
       <c r="U318" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
       <c r="V318" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="W318" s="0" t="s">
         <v>105</v>
@@ -22752,7 +22758,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="U319" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="V319" s="0">
         <v>0.059999999999999998</v>
@@ -22823,10 +22829,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U320" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
       </c>
       <c r="V320" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
       <c r="W320" s="0" t="s">
         <v>133</v>
@@ -22894,10 +22900,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U321" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
       <c r="V321" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
       <c r="W321" s="0" t="s">
         <v>89</v>
@@ -22965,10 +22971,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U322" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="V322" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="W322" s="0" t="s">
         <v>134</v>
@@ -23036,10 +23042,10 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U323" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="V323" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="W323" s="0" t="s">
         <v>135</v>
@@ -23107,10 +23113,10 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="U324" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V324" s="0">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="W324" s="0" t="s">
         <v>136</v>
@@ -23178,10 +23184,10 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="U325" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V325" s="0">
-        <v>0.02</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="W325" s="0" t="s">
         <v>136</v>
@@ -23249,10 +23255,10 @@
         <v>0.070000000000000007</v>
       </c>
       <c r="U326" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="V326" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="W326" s="0" t="s">
         <v>137</v>
@@ -23320,10 +23326,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U327" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="V327" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W327" s="0" t="s">
         <v>136</v>
@@ -23391,10 +23397,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U328" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.076999999999999999</v>
       </c>
       <c r="V328" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="W328" s="0" t="s">
         <v>137</v>
@@ -23462,10 +23468,10 @@
         <v>0.12</v>
       </c>
       <c r="U329" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.050999999999999997</v>
       </c>
       <c r="V329" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="W329" s="0" t="s">
         <v>137</v>
@@ -23533,10 +23539,10 @@
         <v>0.13</v>
       </c>
       <c r="U330" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="V330" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="W330" s="0" t="s">
         <v>136</v>
@@ -23604,10 +23610,10 @@
         <v>0.12</v>
       </c>
       <c r="U331" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="V331" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="W331" s="0" t="s">
         <v>136</v>
@@ -23678,7 +23684,7 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="V332" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
       <c r="W332" s="0" t="s">
         <v>137</v>
@@ -23817,10 +23823,10 @@
         <v>0.12</v>
       </c>
       <c r="U334" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="V334" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="W334" s="0" t="s">
         <v>138</v>
@@ -23888,10 +23894,10 @@
         <v>0.17000000000000001</v>
       </c>
       <c r="U335" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V335" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="W335" s="0" t="s">
         <v>136</v>
@@ -23959,10 +23965,10 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="U336" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="V336" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="W336" s="0" t="s">
         <v>139</v>
@@ -24030,10 +24036,10 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="U337" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V337" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="W337" s="0" t="s">
         <v>140</v>
@@ -24101,10 +24107,10 @@
         <v>0.11</v>
       </c>
       <c r="U338" s="0">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="V338" s="0">
-        <v>0.02</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="W338" s="0" t="s">
         <v>140</v>
@@ -24172,10 +24178,10 @@
         <v>0.11</v>
       </c>
       <c r="U339" s="0">
-        <v>0.01</v>
+        <v>0.012999999999999999</v>
       </c>
       <c r="V339" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W339" s="0" t="s">
         <v>140</v>
@@ -24243,10 +24249,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U340" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V340" s="0">
-        <v>0.02</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="W340" s="0" t="s">
         <v>140</v>
@@ -24314,10 +24320,10 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="U341" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V341" s="0">
-        <v>0.02</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="W341" s="0" t="s">
         <v>140</v>
@@ -24385,10 +24391,10 @@
         <v>0.11</v>
       </c>
       <c r="U342" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V342" s="0">
-        <v>0.02</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="W342" s="0" t="s">
         <v>140</v>
@@ -24456,10 +24462,10 @@
         <v>0.13</v>
       </c>
       <c r="U343" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="V343" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="W343" s="0" t="s">
         <v>140</v>
@@ -24530,7 +24536,7 @@
         <v>0.01</v>
       </c>
       <c r="V344" s="0">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="W344" s="0" t="s">
         <v>140</v>
@@ -24598,10 +24604,10 @@
         <v>0.13</v>
       </c>
       <c r="U345" s="0">
-        <v>0.01</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="V345" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W345" s="0" t="s">
         <v>140</v>
@@ -24669,10 +24675,10 @@
         <v>0.11</v>
       </c>
       <c r="U346" s="0">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="V346" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W346" s="0" t="s">
         <v>140</v>
@@ -24743,7 +24749,7 @@
         <v>0.01</v>
       </c>
       <c r="V347" s="0">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="W347" s="0" t="s">
         <v>140</v>
@@ -24811,10 +24817,10 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="U348" s="0">
-        <v>0.01</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="V348" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="W348" s="0" t="s">
         <v>140</v>
@@ -29626,7 +29632,7 @@
     <col min="10" max="10" width="14.42578125" customWidth="true"/>
     <col min="11" max="11" width="7.28515625" customWidth="true"/>
     <col min="12" max="12" width="10.28515625" customWidth="true"/>
-    <col min="13" max="13" width="15.7109375" customWidth="true"/>
+    <col min="13" max="13" width="12.5703125" customWidth="true"/>
     <col min="14" max="14" width="21.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -29668,7 +29674,7 @@
         <v>19</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N1" s="0" t="s">
         <v>24</v>

--- a/Export/Coring_data_export.xlsx
+++ b/Export/Coring_data_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="114406" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="140342" uniqueCount="188">
   <si>
     <t>Event label</t>
   </si>
@@ -574,6 +574,12 @@
   <si>
     <t>Comments</t>
   </si>
+  <si>
+    <t>Sea ice thickness</t>
+  </si>
+  <si>
+    <t>Sea ice draft</t>
+  </si>
 </sst>
 </file>
 
@@ -625,8 +631,8 @@
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="9.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.28515625" customWidth="true"/>
-    <col min="6" max="6" width="5.7109375" customWidth="true"/>
+    <col min="5" max="5" width="16" customWidth="true"/>
+    <col min="6" max="6" width="12" customWidth="true"/>
     <col min="7" max="7" width="11.42578125" customWidth="true"/>
     <col min="8" max="8" width="18.42578125" customWidth="true"/>
     <col min="9" max="9" width="17.7109375" customWidth="true"/>
@@ -660,10 +666,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="G1" s="0" t="s">
         <v>7</v>
@@ -5760,7 +5766,7 @@
         <v>0.40000000000000002</v>
       </c>
       <c r="O75" s="0">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P75" s="0">
         <v>-23</v>
@@ -5933,7 +5939,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="O78" s="0">
-        <v>1.5</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="P78" s="0">
         <v>-22</v>
@@ -5942,19 +5948,19 @@
         <v>-0.20000000000000001</v>
       </c>
       <c r="R78" s="0">
-        <v>847.75999999999999</v>
+        <v>846.75</v>
       </c>
       <c r="S78" s="0">
-        <v>844.95000000000005</v>
+        <v>843.92999999999995</v>
       </c>
       <c r="T78" s="0">
-        <v>0.34999999999999998</v>
+        <v>0.16</v>
       </c>
       <c r="U78" s="0">
         <v>0.080000000000000002</v>
       </c>
       <c r="V78" s="0">
-        <v>0.111</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="W78" s="0" t="s">
         <v>57</v>
@@ -6004,7 +6010,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="O79" s="0">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="P79" s="0">
         <v>-22</v>
@@ -6013,19 +6019,19 @@
         <v>-0.20000000000000001</v>
       </c>
       <c r="R79" s="0">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="S79" s="0">
-        <v>832.22000000000003</v>
+        <v>831.23000000000002</v>
       </c>
       <c r="T79" s="0">
-        <v>0.34000000000000002</v>
+        <v>0.11</v>
       </c>
       <c r="U79" s="0">
         <v>0.094</v>
       </c>
       <c r="V79" s="0">
-        <v>0.124</v>
+        <v>0.104</v>
       </c>
       <c r="W79" s="0" t="s">
         <v>58</v>
@@ -6075,7 +6081,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O80" s="0">
-        <v>1.2</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="P80" s="0">
         <v>-22</v>
@@ -6084,19 +6090,19 @@
         <v>-0.23000000000000001</v>
       </c>
       <c r="R80" s="0">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="S80" s="0">
-        <v>832.23000000000002</v>
+        <v>831.23000000000002</v>
       </c>
       <c r="T80" s="0">
-        <v>0.23999999999999999</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="U80" s="0">
         <v>0.094</v>
       </c>
       <c r="V80" s="0">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="W80" s="0" t="s">
         <v>59</v>
@@ -6146,7 +6152,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="O81" s="0">
-        <v>0.80000000000000004</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="P81" s="0">
         <v>-22</v>
@@ -6155,19 +6161,19 @@
         <v>-0.28000000000000003</v>
       </c>
       <c r="R81" s="0">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="S81" s="0">
-        <v>832.23000000000002</v>
+        <v>831.24000000000001</v>
       </c>
       <c r="T81" s="0">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="U81" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="V81" s="0">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="W81" s="0" t="s">
         <v>59</v>
@@ -6217,7 +6223,7 @@
         <v>0.25</v>
       </c>
       <c r="O82" s="0">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P82" s="0">
         <v>-22</v>
@@ -6226,16 +6232,16 @@
         <v>-0.38</v>
       </c>
       <c r="R82" s="0">
-        <v>868.41999999999996</v>
+        <v>867.38</v>
       </c>
       <c r="S82" s="0">
-        <v>865.54999999999995</v>
+        <v>864.51999999999998</v>
       </c>
       <c r="T82" s="0">
-        <v>0.16</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="U82" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="V82" s="0">
         <v>0.070999999999999994</v>
@@ -6288,7 +6294,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="O83" s="0">
-        <v>1.8</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="P83" s="0">
         <v>-22</v>
@@ -6297,19 +6303,19 @@
         <v>-0.52000000000000002</v>
       </c>
       <c r="R83" s="0">
-        <v>876.29999999999995</v>
+        <v>875.25</v>
       </c>
       <c r="S83" s="0">
-        <v>873.42999999999995</v>
+        <v>872.38</v>
       </c>
       <c r="T83" s="0">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="U83" s="0">
-        <v>0.049000000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="V83" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="W83" s="0" t="s">
         <v>61</v>
@@ -6359,7 +6365,7 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="O84" s="0">
-        <v>2.3999999999999999</v>
+        <v>2</v>
       </c>
       <c r="P84" s="0">
         <v>-22</v>
@@ -6368,19 +6374,19 @@
         <v>-0.73999999999999999</v>
       </c>
       <c r="R84" s="0">
-        <v>846.17999999999995</v>
+        <v>845.15999999999997</v>
       </c>
       <c r="S84" s="0">
-        <v>843.42999999999995</v>
+        <v>842.41999999999996</v>
       </c>
       <c r="T84" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="U84" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.083000000000000004</v>
       </c>
       <c r="V84" s="0">
-        <v>0.095000000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="W84" s="0" t="s">
         <v>62</v>
@@ -6430,7 +6436,7 @@
         <v>0.40000000000000002</v>
       </c>
       <c r="O85" s="0">
-        <v>2.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="P85" s="0">
         <v>-22</v>
@@ -6439,16 +6445,16 @@
         <v>-0.80000000000000004</v>
       </c>
       <c r="R85" s="0">
-        <v>887.82000000000005</v>
+        <v>886.75</v>
       </c>
       <c r="S85" s="0">
-        <v>884.95000000000005</v>
+        <v>883.88999999999999</v>
       </c>
       <c r="T85" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="U85" s="0">
-        <v>0.036999999999999998</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="V85" s="0">
         <v>0.050000000000000003</v>
@@ -6501,7 +6507,7 @@
         <v>0.45000000000000001</v>
       </c>
       <c r="O86" s="0">
-        <v>3.2000000000000002</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="P86" s="0">
         <v>-22</v>
@@ -6510,19 +6516,19 @@
         <v>-0.83999999999999997</v>
       </c>
       <c r="R86" s="0">
-        <v>850.87</v>
+        <v>849.85000000000002</v>
       </c>
       <c r="S86" s="0">
-        <v>848.12</v>
+        <v>847.10000000000002</v>
       </c>
       <c r="T86" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="U86" s="0">
-        <v>0.078</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="V86" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.091999999999999998</v>
       </c>
       <c r="W86" s="0" t="s">
         <v>64</v>
@@ -6581,19 +6587,19 @@
         <v>-0.89000000000000001</v>
       </c>
       <c r="R87" s="0">
-        <v>900.53999999999996</v>
+        <v>899.47000000000003</v>
       </c>
       <c r="S87" s="0">
-        <v>897.64999999999998</v>
+        <v>896.57000000000005</v>
       </c>
       <c r="T87" s="0">
         <v>0.16</v>
       </c>
       <c r="U87" s="0">
-        <v>0.024</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="V87" s="0">
-        <v>0.037999999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="W87" s="0" t="s">
         <v>65</v>
@@ -6643,7 +6649,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="O88" s="0">
-        <v>3.7999999999999998</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="P88" s="0">
         <v>-22</v>
@@ -6652,19 +6658,19 @@
         <v>-0.94999999999999996</v>
       </c>
       <c r="R88" s="0">
-        <v>905.34000000000003</v>
+        <v>904.25</v>
       </c>
       <c r="S88" s="0">
-        <v>902.42999999999995</v>
+        <v>901.35000000000002</v>
       </c>
       <c r="T88" s="0">
-        <v>0.19</v>
+        <v>0.17000000000000001</v>
       </c>
       <c r="U88" s="0">
         <v>0.02</v>
       </c>
       <c r="V88" s="0">
-        <v>0.035999999999999997</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="W88" s="0" t="s">
         <v>66</v>
@@ -6714,7 +6720,7 @@
         <v>0.62</v>
       </c>
       <c r="O89" s="0">
-        <v>3.2999999999999998</v>
+        <v>2.3999999999999999</v>
       </c>
       <c r="P89" s="0">
         <v>-22</v>
@@ -6723,19 +6729,19 @@
         <v>-1.0800000000000001</v>
       </c>
       <c r="R89" s="0">
-        <v>878.54999999999995</v>
+        <v>877.5</v>
       </c>
       <c r="S89" s="0">
-        <v>875.75</v>
+        <v>874.70000000000005</v>
       </c>
       <c r="T89" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U89" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="V89" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="W89" s="0" t="s">
         <v>66</v>
@@ -6785,7 +6791,7 @@
         <v>0.67000000000000004</v>
       </c>
       <c r="O90" s="0">
-        <v>3.2000000000000002</v>
+        <v>2.8999999999999999</v>
       </c>
       <c r="P90" s="0">
         <v>-22</v>
@@ -6794,16 +6800,16 @@
         <v>-1.3400000000000001</v>
       </c>
       <c r="R90" s="0">
-        <v>896.17999999999995</v>
+        <v>895.10000000000002</v>
       </c>
       <c r="S90" s="0">
-        <v>893.35000000000002</v>
+        <v>892.27999999999997</v>
       </c>
       <c r="T90" s="0">
-        <v>0.11</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="U90" s="0">
-        <v>0.029000000000000001</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="V90" s="0">
         <v>0.039</v>
@@ -6856,7 +6862,7 @@
         <v>0.71999999999999997</v>
       </c>
       <c r="O91" s="0">
-        <v>3.1000000000000001</v>
+        <v>2.6000000000000001</v>
       </c>
       <c r="P91" s="0">
         <v>-22</v>
@@ -6865,19 +6871,19 @@
         <v>-1.5</v>
       </c>
       <c r="R91" s="0">
-        <v>909.44000000000005</v>
+        <v>908.35000000000002</v>
       </c>
       <c r="S91" s="0">
-        <v>906.60000000000002</v>
+        <v>905.50999999999999</v>
       </c>
       <c r="T91" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="U91" s="0">
         <v>0.014999999999999999</v>
       </c>
       <c r="V91" s="0">
-        <v>0.023</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W91" s="0"/>
     </row>
@@ -10835,7 +10841,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O148" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P148" s="0">
         <v>-23</v>
@@ -10850,13 +10856,13 @@
         <v>870.85000000000002</v>
       </c>
       <c r="T148" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="U148" s="0">
         <v>0.050000000000000003</v>
       </c>
       <c r="V148" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="W148" s="0" t="s">
         <v>83</v>
@@ -10902,7 +10908,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="O149" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="P149" s="0">
         <v>-23</v>
@@ -10917,7 +10923,7 @@
         <v>879.41999999999996</v>
       </c>
       <c r="T149" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="U149" s="0">
         <v>0.041000000000000002</v>
@@ -10969,7 +10975,7 @@
         <v>0.25</v>
       </c>
       <c r="O150" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="P150" s="0">
         <v>-23</v>
@@ -10984,13 +10990,13 @@
         <v>883.13</v>
       </c>
       <c r="T150" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="U150" s="0">
         <v>0.036999999999999998</v>
       </c>
       <c r="V150" s="0">
-        <v>0.042000000000000003</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="W150" s="0" t="s">
         <v>61</v>
@@ -15497,7 +15503,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="O216" s="0">
-        <v>0.11</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P216" s="0">
         <v>-21</v>
@@ -15512,10 +15518,10 @@
         <v>868.97000000000003</v>
       </c>
       <c r="T216" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="U216" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="V216" s="0">
         <v>0.055</v>
@@ -15568,7 +15574,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="O217" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="P217" s="0">
         <v>-21</v>
@@ -15583,13 +15589,13 @@
         <v>898.32000000000005</v>
       </c>
       <c r="T217" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="U217" s="0">
         <v>0.02</v>
       </c>
       <c r="V217" s="0">
-        <v>0.023</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W217" s="0" t="s">
         <v>61</v>
@@ -15639,7 +15645,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O218" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="P218" s="0">
         <v>-21</v>
@@ -15654,7 +15660,7 @@
         <v>904.29999999999995</v>
       </c>
       <c r="T218" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="U218" s="0">
         <v>0.014</v>
@@ -20754,7 +20760,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="O291" s="0">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="P291" s="0">
         <v>-22</v>
@@ -20769,13 +20775,13 @@
         <v>850.74000000000001</v>
       </c>
       <c r="T291" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="U291" s="0">
         <v>0.071999999999999995</v>
       </c>
       <c r="V291" s="0">
-        <v>0.078</v>
+        <v>0.076999999999999999</v>
       </c>
       <c r="W291" s="0" t="s">
         <v>126</v>
@@ -22740,7 +22746,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="O319" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="P319" s="0">
         <v>-24</v>
@@ -22755,13 +22761,13 @@
         <v>869.42999999999995</v>
       </c>
       <c r="T319" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="U319" s="0">
         <v>0.051999999999999998</v>
       </c>
       <c r="V319" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="W319" s="0" t="s">
         <v>105</v>
@@ -22882,7 +22888,7 @@
         <v>0.25</v>
       </c>
       <c r="O321" s="0">
-        <v>0.19</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P321" s="0">
         <v>-24</v>
@@ -22897,13 +22903,13 @@
         <v>845.62</v>
       </c>
       <c r="T321" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="U321" s="0">
         <v>0.078</v>
       </c>
       <c r="V321" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="W321" s="0" t="s">
         <v>89</v>
@@ -22953,7 +22959,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="O322" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="P322" s="0">
         <v>-24</v>
@@ -22968,13 +22974,13 @@
         <v>867.24000000000001</v>
       </c>
       <c r="T322" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="U322" s="0">
         <v>0.053999999999999999</v>
       </c>
       <c r="V322" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="W322" s="0" t="s">
         <v>134</v>
@@ -23024,7 +23030,7 @@
         <v>0.34999999999999998</v>
       </c>
       <c r="O323" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="P323" s="0">
         <v>-24</v>
@@ -23039,13 +23045,13 @@
         <v>890.75</v>
       </c>
       <c r="T323" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="U323" s="0">
         <v>0.029000000000000001</v>
       </c>
       <c r="V323" s="0">
-        <v>0.032000000000000001</v>
+        <v>0.031</v>
       </c>
       <c r="W323" s="0" t="s">
         <v>135</v>
@@ -23095,7 +23101,7 @@
         <v>0.40000000000000002</v>
       </c>
       <c r="O324" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="P324" s="0">
         <v>-24</v>
@@ -23110,13 +23116,13 @@
         <v>899.65999999999997</v>
       </c>
       <c r="T324" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="U324" s="0">
         <v>0.019</v>
       </c>
       <c r="V324" s="0">
-        <v>0.024</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="W324" s="0" t="s">
         <v>136</v>
@@ -28374,7 +28380,7 @@
         <v>0.059999999999999998</v>
       </c>
       <c r="O409" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P409" s="0">
         <v>-23</v>
@@ -28435,7 +28441,7 @@
         <v>0.12</v>
       </c>
       <c r="O410" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P410" s="0">
         <v>-23</v>
@@ -28496,7 +28502,7 @@
         <v>0.17999999999999999</v>
       </c>
       <c r="O411" s="0">
-        <v>0.11</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P411" s="0">
         <v>-23</v>
@@ -28557,7 +28563,7 @@
         <v>0.22</v>
       </c>
       <c r="O412" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="P412" s="0">
         <v>-23</v>
@@ -28618,7 +28624,7 @@
         <v>0.27000000000000002</v>
       </c>
       <c r="O413" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="P413" s="0">
         <v>-23</v>
@@ -28679,7 +28685,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="O414" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="P414" s="0">
         <v>-23</v>
@@ -28740,7 +28746,7 @@
         <v>0.39000000000000001</v>
       </c>
       <c r="O415" s="0">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="P415" s="0">
         <v>-23</v>
@@ -28801,7 +28807,7 @@
         <v>0.45000000000000001</v>
       </c>
       <c r="O416" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="P416" s="0">
         <v>-23</v>
@@ -28862,7 +28868,7 @@
         <v>0.51000000000000001</v>
       </c>
       <c r="O417" s="0">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="P417" s="0">
         <v>-23</v>
@@ -28923,7 +28929,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="O418" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="P418" s="0">
         <v>-23</v>
@@ -29411,7 +29417,7 @@
         <v>1.0800000000000001</v>
       </c>
       <c r="O426" s="0">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="P426" s="0">
         <v>-23</v>
@@ -29624,15 +29630,15 @@
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="9.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.28515625" customWidth="true"/>
-    <col min="6" max="6" width="5.7109375" customWidth="true"/>
+    <col min="5" max="5" width="16" customWidth="true"/>
+    <col min="6" max="6" width="12" customWidth="true"/>
     <col min="7" max="7" width="11.42578125" customWidth="true"/>
     <col min="8" max="8" width="15.5703125" customWidth="true"/>
     <col min="9" max="9" width="17.7109375" customWidth="true"/>
     <col min="10" max="10" width="14.42578125" customWidth="true"/>
     <col min="11" max="11" width="7.28515625" customWidth="true"/>
     <col min="12" max="12" width="10.28515625" customWidth="true"/>
-    <col min="13" max="13" width="12.5703125" customWidth="true"/>
+    <col min="13" max="13" width="15.7109375" customWidth="true"/>
     <col min="14" max="14" width="21.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -29650,10 +29656,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="G1" s="0" t="s">
         <v>7</v>
@@ -29674,7 +29680,7 @@
         <v>19</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="N1" s="0" t="s">
         <v>24</v>
@@ -38941,8 +38947,8 @@
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="9.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.28515625" customWidth="true"/>
-    <col min="6" max="6" width="5.5703125" customWidth="true"/>
+    <col min="5" max="5" width="16" customWidth="true"/>
+    <col min="6" max="6" width="12" customWidth="true"/>
     <col min="7" max="7" width="11.42578125" customWidth="true"/>
     <col min="8" max="8" width="21.140625" customWidth="true"/>
     <col min="9" max="9" width="17.7109375" customWidth="true"/>
@@ -38968,10 +38974,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="G1" s="0" t="s">
         <v>7</v>

--- a/Export/Coring_data_export.xlsx
+++ b/Export/Coring_data_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="140342" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="143584" uniqueCount="188">
   <si>
     <t>Event label</t>
   </si>
@@ -39050,7 +39050,9 @@
       <c r="N2" s="0">
         <v>0.050000000000000003</v>
       </c>
-      <c r="O2" s="0"/>
+      <c r="O2" s="0">
+        <v>0.90000000000000002</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -39095,7 +39097,9 @@
       <c r="N3" s="0">
         <v>0.10000000000000001</v>
       </c>
-      <c r="O3" s="0"/>
+      <c r="O3" s="0">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -39140,7 +39144,9 @@
       <c r="N4" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="O4" s="0"/>
+      <c r="O4" s="0">
+        <v>2.1000000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -39185,7 +39191,9 @@
       <c r="N5" s="0">
         <v>0.20000000000000001</v>
       </c>
-      <c r="O5" s="0"/>
+      <c r="O5" s="0">
+        <v>2.3999999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -39230,7 +39238,9 @@
       <c r="N6" s="0">
         <v>0.25</v>
       </c>
-      <c r="O6" s="0"/>
+      <c r="O6" s="0">
+        <v>2.7999999999999998</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -39275,7 +39285,9 @@
       <c r="N7" s="0">
         <v>0.29999999999999999</v>
       </c>
-      <c r="O7" s="0"/>
+      <c r="O7" s="0">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -39320,7 +39332,9 @@
       <c r="N8" s="0">
         <v>0.34000000000000002</v>
       </c>
-      <c r="O8" s="0"/>
+      <c r="O8" s="0">
+        <v>3.7999999999999998</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -39365,7 +39379,9 @@
       <c r="N9" s="0">
         <v>0.39000000000000001</v>
       </c>
-      <c r="O9" s="0"/>
+      <c r="O9" s="0">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
@@ -39410,7 +39426,9 @@
       <c r="N10" s="0">
         <v>0.44</v>
       </c>
-      <c r="O10" s="0"/>
+      <c r="O10" s="0">
+        <v>4.2000000000000002</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -39455,7 +39473,9 @@
       <c r="N11" s="0">
         <v>0.48999999999999999</v>
       </c>
-      <c r="O11" s="0"/>
+      <c r="O11" s="0">
+        <v>3.8999999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -39500,7 +39520,9 @@
       <c r="N12" s="0">
         <v>0.54000000000000004</v>
       </c>
-      <c r="O12" s="0"/>
+      <c r="O12" s="0">
+        <v>4.7000000000000002</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -39545,7 +39567,9 @@
       <c r="N13" s="0">
         <v>0.58999999999999997</v>
       </c>
-      <c r="O13" s="0"/>
+      <c r="O13" s="0">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -39590,7 +39614,9 @@
       <c r="N14" s="0">
         <v>0.64000000000000001</v>
       </c>
-      <c r="O14" s="0"/>
+      <c r="O14" s="0">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -39635,7 +39661,9 @@
       <c r="N15" s="0">
         <v>0.68999999999999995</v>
       </c>
-      <c r="O15" s="0"/>
+      <c r="O15" s="0">
+        <v>3.7000000000000002</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -39680,7 +39708,9 @@
       <c r="N16" s="0">
         <v>0.73999999999999999</v>
       </c>
-      <c r="O16" s="0"/>
+      <c r="O16" s="0">
+        <v>3.7000000000000002</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
